--- a/add-in-ids/add-ins-using-exchange-tokens.xlsx
+++ b/add-in-ids/add-ins-using-exchange-tokens.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C71497-A64B-4E37-AA78-608A70459B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FFD934-5A53-4CAA-A286-4A76F2C0EACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
+    <workbookView xWindow="4230" yWindow="1035" windowWidth="18180" windowHeight="14130" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
   </bookViews>
   <sheets>
     <sheet name="Add-ins list" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="2625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="2622">
   <si>
     <t>AssetID</t>
   </si>
@@ -2296,15 +2296,6 @@
   </si>
   <si>
     <t>iCIMS Video Studio</t>
-  </si>
-  <si>
-    <t>wa200000033</t>
-  </si>
-  <si>
-    <t>f762dd1f-92c5-486c-992f-31a61967279d</t>
-  </si>
-  <si>
-    <t>Traction Guest</t>
   </si>
   <si>
     <t>wa200000035</t>
@@ -7990,8 +7981,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C913" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:C913" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C912" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:C912" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{39B649A1-0CDF-46AA-A276-6F4F89255D96}" name="AssetID"/>
     <tableColumn id="2" xr3:uid="{C79A1EFF-47FF-488B-A562-E9848648C952}" name="AppId"/>
@@ -8318,7 +8309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3293B4AA-89CE-4E6A-9112-DA5B905DDA88}">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -8332,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2624</v>
+        <v>2621</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -11389,15 +11380,15 @@
         <v>830</v>
       </c>
       <c r="B280" t="s">
-        <v>831</v>
+        <v>281</v>
       </c>
       <c r="C280" t="s">
-        <v>832</v>
+        <v>282</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B281" t="s">
         <v>281</v>
@@ -11408,7 +11399,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B282" t="s">
         <v>281</v>
@@ -11419,7 +11410,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B283" t="s">
         <v>281</v>
@@ -11430,7 +11421,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B284" t="s">
         <v>281</v>
@@ -11441,7 +11432,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B285" t="s">
         <v>281</v>
@@ -11452,13 +11443,13 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>836</v>
+      </c>
+      <c r="B286" t="s">
+        <v>837</v>
+      </c>
+      <c r="C286" t="s">
         <v>838</v>
-      </c>
-      <c r="B286" t="s">
-        <v>281</v>
-      </c>
-      <c r="C286" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -11477,15 +11468,15 @@
         <v>842</v>
       </c>
       <c r="B288" t="s">
-        <v>843</v>
+        <v>281</v>
       </c>
       <c r="C288" t="s">
-        <v>844</v>
+        <v>282</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B289" t="s">
         <v>281</v>
@@ -11496,7 +11487,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B290" t="s">
         <v>281</v>
@@ -11507,7 +11498,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B291" t="s">
         <v>281</v>
@@ -11518,13 +11509,13 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>846</v>
+      </c>
+      <c r="B292" t="s">
+        <v>847</v>
+      </c>
+      <c r="C292" t="s">
         <v>848</v>
-      </c>
-      <c r="B292" t="s">
-        <v>281</v>
-      </c>
-      <c r="C292" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -11543,21 +11534,21 @@
         <v>852</v>
       </c>
       <c r="B294" t="s">
-        <v>853</v>
+        <v>281</v>
       </c>
       <c r="C294" t="s">
-        <v>854</v>
+        <v>282</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
+        <v>853</v>
+      </c>
+      <c r="B295" t="s">
+        <v>854</v>
+      </c>
+      <c r="C295" t="s">
         <v>855</v>
-      </c>
-      <c r="B295" t="s">
-        <v>281</v>
-      </c>
-      <c r="C295" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -11565,15 +11556,15 @@
         <v>856</v>
       </c>
       <c r="B296" t="s">
-        <v>857</v>
+        <v>281</v>
       </c>
       <c r="C296" t="s">
-        <v>858</v>
+        <v>282</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B297" t="s">
         <v>281</v>
@@ -11584,13 +11575,13 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
+        <v>858</v>
+      </c>
+      <c r="B298" t="s">
+        <v>859</v>
+      </c>
+      <c r="C298" t="s">
         <v>860</v>
-      </c>
-      <c r="B298" t="s">
-        <v>281</v>
-      </c>
-      <c r="C298" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -11653,21 +11644,21 @@
         <v>876</v>
       </c>
       <c r="B304" t="s">
-        <v>877</v>
+        <v>281</v>
       </c>
       <c r="C304" t="s">
-        <v>878</v>
+        <v>282</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
+        <v>877</v>
+      </c>
+      <c r="B305" t="s">
+        <v>878</v>
+      </c>
+      <c r="C305" t="s">
         <v>879</v>
-      </c>
-      <c r="B305" t="s">
-        <v>281</v>
-      </c>
-      <c r="C305" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -11675,15 +11666,15 @@
         <v>880</v>
       </c>
       <c r="B306" t="s">
-        <v>881</v>
+        <v>281</v>
       </c>
       <c r="C306" t="s">
-        <v>882</v>
+        <v>282</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B307" t="s">
         <v>281</v>
@@ -11694,7 +11685,7 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B308" t="s">
         <v>281</v>
@@ -11705,7 +11696,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B309" t="s">
         <v>281</v>
@@ -11716,7 +11707,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B310" t="s">
         <v>281</v>
@@ -11727,7 +11718,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B311" t="s">
         <v>281</v>
@@ -11738,7 +11729,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B312" t="s">
         <v>281</v>
@@ -11749,7 +11740,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B313" t="s">
         <v>281</v>
@@ -11760,7 +11751,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B314" t="s">
         <v>281</v>
@@ -11771,7 +11762,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B315" t="s">
         <v>281</v>
@@ -11782,7 +11773,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B316" t="s">
         <v>281</v>
@@ -11793,7 +11784,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B317" t="s">
         <v>281</v>
@@ -11804,7 +11795,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B318" t="s">
         <v>281</v>
@@ -11815,7 +11806,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B319" t="s">
         <v>281</v>
@@ -11826,7 +11817,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B320" t="s">
         <v>281</v>
@@ -11837,7 +11828,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B321" t="s">
         <v>281</v>
@@ -11848,7 +11839,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B322" t="s">
         <v>281</v>
@@ -11859,7 +11850,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B323" t="s">
         <v>281</v>
@@ -11870,7 +11861,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B324" t="s">
         <v>281</v>
@@ -11881,7 +11872,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B325" t="s">
         <v>281</v>
@@ -11892,7 +11883,7 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B326" t="s">
         <v>281</v>
@@ -11903,7 +11894,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B327" t="s">
         <v>281</v>
@@ -11914,13 +11905,13 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>902</v>
+      </c>
+      <c r="B328" t="s">
+        <v>903</v>
+      </c>
+      <c r="C328" t="s">
         <v>904</v>
-      </c>
-      <c r="B328" t="s">
-        <v>281</v>
-      </c>
-      <c r="C328" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -11928,15 +11919,15 @@
         <v>905</v>
       </c>
       <c r="B329" t="s">
-        <v>906</v>
+        <v>281</v>
       </c>
       <c r="C329" t="s">
-        <v>907</v>
+        <v>282</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B330" t="s">
         <v>281</v>
@@ -11947,7 +11938,7 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B331" t="s">
         <v>281</v>
@@ -11958,7 +11949,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B332" t="s">
         <v>281</v>
@@ -11969,7 +11960,7 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B333" t="s">
         <v>281</v>
@@ -11980,13 +11971,13 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
+        <v>910</v>
+      </c>
+      <c r="B334" t="s">
+        <v>911</v>
+      </c>
+      <c r="C334" t="s">
         <v>912</v>
-      </c>
-      <c r="B334" t="s">
-        <v>281</v>
-      </c>
-      <c r="C334" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -11994,15 +11985,15 @@
         <v>913</v>
       </c>
       <c r="B335" t="s">
-        <v>914</v>
+        <v>281</v>
       </c>
       <c r="C335" t="s">
-        <v>915</v>
+        <v>282</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B336" t="s">
         <v>281</v>
@@ -12013,13 +12004,13 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>915</v>
+      </c>
+      <c r="B337" t="s">
+        <v>916</v>
+      </c>
+      <c r="C337" t="s">
         <v>917</v>
-      </c>
-      <c r="B337" t="s">
-        <v>281</v>
-      </c>
-      <c r="C337" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -12052,18 +12043,18 @@
         <v>925</v>
       </c>
       <c r="C340" t="s">
-        <v>926</v>
+        <v>282</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
+        <v>926</v>
+      </c>
+      <c r="B341" t="s">
         <v>927</v>
       </c>
-      <c r="B341" t="s">
+      <c r="C341" t="s">
         <v>928</v>
-      </c>
-      <c r="C341" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -12283,18 +12274,18 @@
         <v>987</v>
       </c>
       <c r="C361" t="s">
-        <v>988</v>
+        <v>282</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>988</v>
+      </c>
+      <c r="B362" t="s">
         <v>989</v>
       </c>
-      <c r="B362" t="s">
+      <c r="C362" t="s">
         <v>990</v>
-      </c>
-      <c r="C362" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -12302,21 +12293,21 @@
         <v>991</v>
       </c>
       <c r="B363" t="s">
-        <v>992</v>
+        <v>38</v>
       </c>
       <c r="C363" t="s">
-        <v>993</v>
+        <v>39</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
+        <v>992</v>
+      </c>
+      <c r="B364" t="s">
+        <v>993</v>
+      </c>
+      <c r="C364" t="s">
         <v>994</v>
-      </c>
-      <c r="B364" t="s">
-        <v>38</v>
-      </c>
-      <c r="C364" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -12324,21 +12315,21 @@
         <v>995</v>
       </c>
       <c r="B365" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C365" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>996</v>
+      </c>
+      <c r="B366" t="s">
+        <v>997</v>
+      </c>
+      <c r="C366" t="s">
         <v>998</v>
-      </c>
-      <c r="B366" t="s">
-        <v>996</v>
-      </c>
-      <c r="C366" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -12632,29 +12623,29 @@
         <v>1077</v>
       </c>
       <c r="B393" t="s">
-        <v>1078</v>
+        <v>987</v>
       </c>
       <c r="C393" t="s">
-        <v>1079</v>
+        <v>282</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B394" t="s">
-        <v>990</v>
+        <v>203</v>
       </c>
       <c r="C394" t="s">
-        <v>282</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B395" t="s">
         <v>1081</v>
-      </c>
-      <c r="B395" t="s">
-        <v>203</v>
       </c>
       <c r="C395" t="s">
         <v>1082</v>
@@ -12874,18 +12865,18 @@
         <v>1140</v>
       </c>
       <c r="B415" t="s">
+        <v>634</v>
+      </c>
+      <c r="C415" t="s">
         <v>1141</v>
-      </c>
-      <c r="C415" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B416" t="s">
         <v>1143</v>
-      </c>
-      <c r="B416" t="s">
-        <v>634</v>
       </c>
       <c r="C416" t="s">
         <v>1144</v>
@@ -12972,7 +12963,7 @@
       <c r="A424" t="s">
         <v>1166</v>
       </c>
-      <c r="B424" t="s">
+      <c r="B424" s="1" t="s">
         <v>1167</v>
       </c>
       <c r="C424" t="s">
@@ -12983,7 +12974,7 @@
       <c r="A425" t="s">
         <v>1169</v>
       </c>
-      <c r="B425" s="1" t="s">
+      <c r="B425" t="s">
         <v>1170</v>
       </c>
       <c r="C425" t="s">
@@ -13104,7 +13095,7 @@
       <c r="A436" t="s">
         <v>1202</v>
       </c>
-      <c r="B436" t="s">
+      <c r="B436" s="1" t="s">
         <v>1203</v>
       </c>
       <c r="C436" t="s">
@@ -13115,7 +13106,7 @@
       <c r="A437" t="s">
         <v>1205</v>
       </c>
-      <c r="B437" s="1" t="s">
+      <c r="B437" t="s">
         <v>1206</v>
       </c>
       <c r="C437" t="s">
@@ -13192,7 +13183,7 @@
       <c r="A444" t="s">
         <v>1226</v>
       </c>
-      <c r="B444" t="s">
+      <c r="B444" s="1" t="s">
         <v>1227</v>
       </c>
       <c r="C444" t="s">
@@ -13203,7 +13194,7 @@
       <c r="A445" t="s">
         <v>1229</v>
       </c>
-      <c r="B445" s="1" t="s">
+      <c r="B445" t="s">
         <v>1230</v>
       </c>
       <c r="C445" t="s">
@@ -13412,7 +13403,7 @@
       <c r="A464" t="s">
         <v>1286</v>
       </c>
-      <c r="B464" t="s">
+      <c r="B464" s="1" t="s">
         <v>1287</v>
       </c>
       <c r="C464" t="s">
@@ -13423,7 +13414,7 @@
       <c r="A465" t="s">
         <v>1289</v>
       </c>
-      <c r="B465" s="1" t="s">
+      <c r="B465" t="s">
         <v>1290</v>
       </c>
       <c r="C465" t="s">
@@ -13555,7 +13546,7 @@
       <c r="A477" t="s">
         <v>1325</v>
       </c>
-      <c r="B477" t="s">
+      <c r="B477" s="1" t="s">
         <v>1326</v>
       </c>
       <c r="C477" t="s">
@@ -13566,7 +13557,7 @@
       <c r="A478" t="s">
         <v>1328</v>
       </c>
-      <c r="B478" s="1" t="s">
+      <c r="B478" t="s">
         <v>1329</v>
       </c>
       <c r="C478" t="s">
@@ -13597,13 +13588,13 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B481" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C481" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -13633,21 +13624,21 @@
         <v>1347</v>
       </c>
       <c r="B484" t="s">
-        <v>1348</v>
+        <v>987</v>
       </c>
       <c r="C484" t="s">
-        <v>1349</v>
+        <v>282</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C485" t="s">
         <v>1350</v>
-      </c>
-      <c r="B485" t="s">
-        <v>990</v>
-      </c>
-      <c r="C485" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -14230,18 +14221,18 @@
         <v>1508</v>
       </c>
       <c r="C538" t="s">
-        <v>1509</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B539" t="s">
         <v>1510</v>
       </c>
-      <c r="B539" t="s">
+      <c r="C539" t="s">
         <v>1511</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -14249,18 +14240,18 @@
         <v>1512</v>
       </c>
       <c r="B540" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C540" t="s">
         <v>1513</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1514</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B541" t="s">
         <v>1515</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1499</v>
       </c>
       <c r="C541" t="s">
         <v>1516</v>
@@ -14700,18 +14691,18 @@
         <v>1634</v>
       </c>
       <c r="B581" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C581" t="s">
         <v>1635</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B582" t="s">
         <v>1637</v>
-      </c>
-      <c r="B582" t="s">
-        <v>1499</v>
       </c>
       <c r="C582" t="s">
         <v>1638</v>
@@ -15176,18 +15167,18 @@
         <v>1763</v>
       </c>
       <c r="C624" t="s">
-        <v>1764</v>
+        <v>614</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B625" t="s">
         <v>1765</v>
       </c>
-      <c r="B625" t="s">
+      <c r="C625" t="s">
         <v>1766</v>
-      </c>
-      <c r="C625" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -15594,18 +15585,18 @@
         <v>1876</v>
       </c>
       <c r="C662" t="s">
-        <v>1877</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B663" t="s">
         <v>1878</v>
       </c>
-      <c r="B663" t="s">
+      <c r="C663" t="s">
         <v>1879</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -15814,18 +15805,18 @@
         <v>1935</v>
       </c>
       <c r="C682" t="s">
-        <v>1936</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B683" t="s">
         <v>1937</v>
       </c>
-      <c r="B683" t="s">
+      <c r="C683" t="s">
         <v>1938</v>
-      </c>
-      <c r="C683" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -16606,18 +16597,18 @@
         <v>2150</v>
       </c>
       <c r="C754" t="s">
-        <v>2151</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B755" t="s">
         <v>2152</v>
       </c>
-      <c r="B755" t="s">
+      <c r="C755" t="s">
         <v>2153</v>
-      </c>
-      <c r="C755" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.25">
@@ -16694,18 +16685,18 @@
         <v>2173</v>
       </c>
       <c r="C762" t="s">
-        <v>2174</v>
+        <v>294</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B763" t="s">
         <v>2175</v>
       </c>
-      <c r="B763" t="s">
+      <c r="C763" t="s">
         <v>2176</v>
-      </c>
-      <c r="C763" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.25">
@@ -16727,18 +16718,18 @@
         <v>2181</v>
       </c>
       <c r="C765" t="s">
-        <v>2182</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B766" t="s">
         <v>2183</v>
       </c>
-      <c r="B766" t="s">
+      <c r="C766" t="s">
         <v>2184</v>
-      </c>
-      <c r="C766" t="s">
-        <v>1525</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.25">
@@ -16859,18 +16850,18 @@
         <v>2216</v>
       </c>
       <c r="C777" t="s">
-        <v>2217</v>
+        <v>497</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B778" t="s">
         <v>2218</v>
       </c>
-      <c r="B778" t="s">
+      <c r="C778" t="s">
         <v>2219</v>
-      </c>
-      <c r="C778" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.25">
@@ -17750,18 +17741,18 @@
         <v>2458</v>
       </c>
       <c r="C858" t="s">
-        <v>2459</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B859" t="s">
         <v>2460</v>
       </c>
-      <c r="B859" t="s">
+      <c r="C859" t="s">
         <v>2461</v>
-      </c>
-      <c r="C859" t="s">
-        <v>2444</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.25">
@@ -18345,17 +18336,6 @@
       </c>
       <c r="C912" t="s">
         <v>2620</v>
-      </c>
-    </row>
-    <row r="913" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A913" t="s">
-        <v>2621</v>
-      </c>
-      <c r="B913" t="s">
-        <v>2622</v>
-      </c>
-      <c r="C913" t="s">
-        <v>2623</v>
       </c>
     </row>
   </sheetData>

--- a/add-in-ids/add-ins-using-exchange-tokens.xlsx
+++ b/add-in-ids/add-ins-using-exchange-tokens.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FFD934-5A53-4CAA-A286-4A76F2C0EACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9BDEF2-8F23-4ECC-BD34-7BD727B64A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="1035" windowWidth="18180" windowHeight="14130" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
+    <workbookView xWindow="19395" yWindow="465" windowWidth="18180" windowHeight="14130" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
   </bookViews>
   <sheets>
     <sheet name="Add-ins list" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="2622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="2619">
   <si>
     <t>AssetID</t>
   </si>
@@ -3790,15 +3790,6 @@
   </si>
   <si>
     <t>Salesforce Connector</t>
-  </si>
-  <si>
-    <t>wa200002298</t>
-  </si>
-  <si>
-    <t>454185ec-7334-4b9b-96c1-5a32f7462d0e</t>
-  </si>
-  <si>
-    <t>Affinity for Outlook</t>
   </si>
   <si>
     <t>wa200002312</t>
@@ -7981,8 +7972,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C912" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:C912" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C911" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:C911" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{39B649A1-0CDF-46AA-A276-6F4F89255D96}" name="AssetID"/>
     <tableColumn id="2" xr3:uid="{C79A1EFF-47FF-488B-A562-E9848648C952}" name="AppId"/>
@@ -8309,7 +8300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3293B4AA-89CE-4E6A-9112-DA5B905DDA88}">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -8323,7 +8314,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -13392,7 +13383,7 @@
       <c r="A463" t="s">
         <v>1283</v>
       </c>
-      <c r="B463" t="s">
+      <c r="B463" s="1" t="s">
         <v>1284</v>
       </c>
       <c r="C463" t="s">
@@ -13403,7 +13394,7 @@
       <c r="A464" t="s">
         <v>1286</v>
       </c>
-      <c r="B464" s="1" t="s">
+      <c r="B464" t="s">
         <v>1287</v>
       </c>
       <c r="C464" t="s">
@@ -13535,7 +13526,7 @@
       <c r="A476" t="s">
         <v>1322</v>
       </c>
-      <c r="B476" t="s">
+      <c r="B476" s="1" t="s">
         <v>1323</v>
       </c>
       <c r="C476" t="s">
@@ -13546,7 +13537,7 @@
       <c r="A477" t="s">
         <v>1325</v>
       </c>
-      <c r="B477" s="1" t="s">
+      <c r="B477" t="s">
         <v>1326</v>
       </c>
       <c r="C477" t="s">
@@ -13577,13 +13568,13 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B480" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C480" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -13613,21 +13604,21 @@
         <v>1344</v>
       </c>
       <c r="B483" t="s">
-        <v>1345</v>
+        <v>987</v>
       </c>
       <c r="C483" t="s">
-        <v>1346</v>
+        <v>282</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C484" t="s">
         <v>1347</v>
-      </c>
-      <c r="B484" t="s">
-        <v>987</v>
-      </c>
-      <c r="C484" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -14210,18 +14201,18 @@
         <v>1505</v>
       </c>
       <c r="C537" t="s">
-        <v>1506</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B538" t="s">
         <v>1507</v>
       </c>
-      <c r="B538" t="s">
+      <c r="C538" t="s">
         <v>1508</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -14229,18 +14220,18 @@
         <v>1509</v>
       </c>
       <c r="B539" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C539" t="s">
         <v>1510</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B540" t="s">
         <v>1512</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1496</v>
       </c>
       <c r="C540" t="s">
         <v>1513</v>
@@ -14680,18 +14671,18 @@
         <v>1631</v>
       </c>
       <c r="B580" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C580" t="s">
         <v>1632</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B581" t="s">
         <v>1634</v>
-      </c>
-      <c r="B581" t="s">
-        <v>1496</v>
       </c>
       <c r="C581" t="s">
         <v>1635</v>
@@ -15156,18 +15147,18 @@
         <v>1760</v>
       </c>
       <c r="C623" t="s">
-        <v>1761</v>
+        <v>614</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B624" t="s">
         <v>1762</v>
       </c>
-      <c r="B624" t="s">
+      <c r="C624" t="s">
         <v>1763</v>
-      </c>
-      <c r="C624" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -15574,18 +15565,18 @@
         <v>1873</v>
       </c>
       <c r="C661" t="s">
-        <v>1874</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B662" t="s">
         <v>1875</v>
       </c>
-      <c r="B662" t="s">
+      <c r="C662" t="s">
         <v>1876</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -15794,18 +15785,18 @@
         <v>1932</v>
       </c>
       <c r="C681" t="s">
-        <v>1933</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B682" t="s">
         <v>1934</v>
       </c>
-      <c r="B682" t="s">
+      <c r="C682" t="s">
         <v>1935</v>
-      </c>
-      <c r="C682" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -16586,18 +16577,18 @@
         <v>2147</v>
       </c>
       <c r="C753" t="s">
-        <v>2148</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B754" t="s">
         <v>2149</v>
       </c>
-      <c r="B754" t="s">
+      <c r="C754" t="s">
         <v>2150</v>
-      </c>
-      <c r="C754" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.25">
@@ -16674,18 +16665,18 @@
         <v>2170</v>
       </c>
       <c r="C761" t="s">
-        <v>2171</v>
+        <v>294</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B762" t="s">
         <v>2172</v>
       </c>
-      <c r="B762" t="s">
+      <c r="C762" t="s">
         <v>2173</v>
-      </c>
-      <c r="C762" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.25">
@@ -16707,18 +16698,18 @@
         <v>2178</v>
       </c>
       <c r="C764" t="s">
-        <v>2179</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B765" t="s">
         <v>2180</v>
       </c>
-      <c r="B765" t="s">
+      <c r="C765" t="s">
         <v>2181</v>
-      </c>
-      <c r="C765" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.25">
@@ -16839,18 +16830,18 @@
         <v>2213</v>
       </c>
       <c r="C776" t="s">
-        <v>2214</v>
+        <v>497</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B777" t="s">
         <v>2215</v>
       </c>
-      <c r="B777" t="s">
+      <c r="C777" t="s">
         <v>2216</v>
-      </c>
-      <c r="C777" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.25">
@@ -17730,18 +17721,18 @@
         <v>2455</v>
       </c>
       <c r="C857" t="s">
-        <v>2456</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B858" t="s">
         <v>2457</v>
       </c>
-      <c r="B858" t="s">
+      <c r="C858" t="s">
         <v>2458</v>
-      </c>
-      <c r="C858" t="s">
-        <v>2441</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.25">
@@ -18325,17 +18316,6 @@
       </c>
       <c r="C911" t="s">
         <v>2617</v>
-      </c>
-    </row>
-    <row r="912" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A912" t="s">
-        <v>2618</v>
-      </c>
-      <c r="B912" t="s">
-        <v>2619</v>
-      </c>
-      <c r="C912" t="s">
-        <v>2620</v>
       </c>
     </row>
   </sheetData>

--- a/add-in-ids/add-ins-using-exchange-tokens.xlsx
+++ b/add-in-ids/add-ins-using-exchange-tokens.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C71497-A64B-4E37-AA78-608A70459B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9BDEF2-8F23-4ECC-BD34-7BD727B64A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
+    <workbookView xWindow="19395" yWindow="465" windowWidth="18180" windowHeight="14130" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
   </bookViews>
   <sheets>
     <sheet name="Add-ins list" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="2625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="2619">
   <si>
     <t>AssetID</t>
   </si>
@@ -2298,15 +2298,6 @@
     <t>iCIMS Video Studio</t>
   </si>
   <si>
-    <t>wa200000033</t>
-  </si>
-  <si>
-    <t>f762dd1f-92c5-486c-992f-31a61967279d</t>
-  </si>
-  <si>
-    <t>Traction Guest</t>
-  </si>
-  <si>
     <t>wa200000035</t>
   </si>
   <si>
@@ -3799,15 +3790,6 @@
   </si>
   <si>
     <t>Salesforce Connector</t>
-  </si>
-  <si>
-    <t>wa200002298</t>
-  </si>
-  <si>
-    <t>454185ec-7334-4b9b-96c1-5a32f7462d0e</t>
-  </si>
-  <si>
-    <t>Affinity for Outlook</t>
   </si>
   <si>
     <t>wa200002312</t>
@@ -7990,8 +7972,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C913" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:C913" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C911" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:C911" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{39B649A1-0CDF-46AA-A276-6F4F89255D96}" name="AssetID"/>
     <tableColumn id="2" xr3:uid="{C79A1EFF-47FF-488B-A562-E9848648C952}" name="AppId"/>
@@ -8318,7 +8300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3293B4AA-89CE-4E6A-9112-DA5B905DDA88}">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -8332,7 +8314,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2624</v>
+        <v>2618</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -11389,15 +11371,15 @@
         <v>830</v>
       </c>
       <c r="B280" t="s">
-        <v>831</v>
+        <v>281</v>
       </c>
       <c r="C280" t="s">
-        <v>832</v>
+        <v>282</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B281" t="s">
         <v>281</v>
@@ -11408,7 +11390,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B282" t="s">
         <v>281</v>
@@ -11419,7 +11401,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B283" t="s">
         <v>281</v>
@@ -11430,7 +11412,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B284" t="s">
         <v>281</v>
@@ -11441,7 +11423,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B285" t="s">
         <v>281</v>
@@ -11452,13 +11434,13 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>836</v>
+      </c>
+      <c r="B286" t="s">
+        <v>837</v>
+      </c>
+      <c r="C286" t="s">
         <v>838</v>
-      </c>
-      <c r="B286" t="s">
-        <v>281</v>
-      </c>
-      <c r="C286" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -11477,15 +11459,15 @@
         <v>842</v>
       </c>
       <c r="B288" t="s">
-        <v>843</v>
+        <v>281</v>
       </c>
       <c r="C288" t="s">
-        <v>844</v>
+        <v>282</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B289" t="s">
         <v>281</v>
@@ -11496,7 +11478,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B290" t="s">
         <v>281</v>
@@ -11507,7 +11489,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B291" t="s">
         <v>281</v>
@@ -11518,13 +11500,13 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>846</v>
+      </c>
+      <c r="B292" t="s">
+        <v>847</v>
+      </c>
+      <c r="C292" t="s">
         <v>848</v>
-      </c>
-      <c r="B292" t="s">
-        <v>281</v>
-      </c>
-      <c r="C292" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -11543,21 +11525,21 @@
         <v>852</v>
       </c>
       <c r="B294" t="s">
-        <v>853</v>
+        <v>281</v>
       </c>
       <c r="C294" t="s">
-        <v>854</v>
+        <v>282</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
+        <v>853</v>
+      </c>
+      <c r="B295" t="s">
+        <v>854</v>
+      </c>
+      <c r="C295" t="s">
         <v>855</v>
-      </c>
-      <c r="B295" t="s">
-        <v>281</v>
-      </c>
-      <c r="C295" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -11565,15 +11547,15 @@
         <v>856</v>
       </c>
       <c r="B296" t="s">
-        <v>857</v>
+        <v>281</v>
       </c>
       <c r="C296" t="s">
-        <v>858</v>
+        <v>282</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B297" t="s">
         <v>281</v>
@@ -11584,13 +11566,13 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
+        <v>858</v>
+      </c>
+      <c r="B298" t="s">
+        <v>859</v>
+      </c>
+      <c r="C298" t="s">
         <v>860</v>
-      </c>
-      <c r="B298" t="s">
-        <v>281</v>
-      </c>
-      <c r="C298" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -11653,21 +11635,21 @@
         <v>876</v>
       </c>
       <c r="B304" t="s">
-        <v>877</v>
+        <v>281</v>
       </c>
       <c r="C304" t="s">
-        <v>878</v>
+        <v>282</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
+        <v>877</v>
+      </c>
+      <c r="B305" t="s">
+        <v>878</v>
+      </c>
+      <c r="C305" t="s">
         <v>879</v>
-      </c>
-      <c r="B305" t="s">
-        <v>281</v>
-      </c>
-      <c r="C305" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -11675,15 +11657,15 @@
         <v>880</v>
       </c>
       <c r="B306" t="s">
-        <v>881</v>
+        <v>281</v>
       </c>
       <c r="C306" t="s">
-        <v>882</v>
+        <v>282</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B307" t="s">
         <v>281</v>
@@ -11694,7 +11676,7 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B308" t="s">
         <v>281</v>
@@ -11705,7 +11687,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B309" t="s">
         <v>281</v>
@@ -11716,7 +11698,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B310" t="s">
         <v>281</v>
@@ -11727,7 +11709,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B311" t="s">
         <v>281</v>
@@ -11738,7 +11720,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B312" t="s">
         <v>281</v>
@@ -11749,7 +11731,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B313" t="s">
         <v>281</v>
@@ -11760,7 +11742,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B314" t="s">
         <v>281</v>
@@ -11771,7 +11753,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B315" t="s">
         <v>281</v>
@@ -11782,7 +11764,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B316" t="s">
         <v>281</v>
@@ -11793,7 +11775,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B317" t="s">
         <v>281</v>
@@ -11804,7 +11786,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B318" t="s">
         <v>281</v>
@@ -11815,7 +11797,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B319" t="s">
         <v>281</v>
@@ -11826,7 +11808,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B320" t="s">
         <v>281</v>
@@ -11837,7 +11819,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B321" t="s">
         <v>281</v>
@@ -11848,7 +11830,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B322" t="s">
         <v>281</v>
@@ -11859,7 +11841,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B323" t="s">
         <v>281</v>
@@ -11870,7 +11852,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B324" t="s">
         <v>281</v>
@@ -11881,7 +11863,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B325" t="s">
         <v>281</v>
@@ -11892,7 +11874,7 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B326" t="s">
         <v>281</v>
@@ -11903,7 +11885,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B327" t="s">
         <v>281</v>
@@ -11914,13 +11896,13 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>902</v>
+      </c>
+      <c r="B328" t="s">
+        <v>903</v>
+      </c>
+      <c r="C328" t="s">
         <v>904</v>
-      </c>
-      <c r="B328" t="s">
-        <v>281</v>
-      </c>
-      <c r="C328" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -11928,15 +11910,15 @@
         <v>905</v>
       </c>
       <c r="B329" t="s">
-        <v>906</v>
+        <v>281</v>
       </c>
       <c r="C329" t="s">
-        <v>907</v>
+        <v>282</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B330" t="s">
         <v>281</v>
@@ -11947,7 +11929,7 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B331" t="s">
         <v>281</v>
@@ -11958,7 +11940,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B332" t="s">
         <v>281</v>
@@ -11969,7 +11951,7 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B333" t="s">
         <v>281</v>
@@ -11980,13 +11962,13 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
+        <v>910</v>
+      </c>
+      <c r="B334" t="s">
+        <v>911</v>
+      </c>
+      <c r="C334" t="s">
         <v>912</v>
-      </c>
-      <c r="B334" t="s">
-        <v>281</v>
-      </c>
-      <c r="C334" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -11994,15 +11976,15 @@
         <v>913</v>
       </c>
       <c r="B335" t="s">
-        <v>914</v>
+        <v>281</v>
       </c>
       <c r="C335" t="s">
-        <v>915</v>
+        <v>282</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B336" t="s">
         <v>281</v>
@@ -12013,13 +11995,13 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>915</v>
+      </c>
+      <c r="B337" t="s">
+        <v>916</v>
+      </c>
+      <c r="C337" t="s">
         <v>917</v>
-      </c>
-      <c r="B337" t="s">
-        <v>281</v>
-      </c>
-      <c r="C337" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -12052,18 +12034,18 @@
         <v>925</v>
       </c>
       <c r="C340" t="s">
-        <v>926</v>
+        <v>282</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
+        <v>926</v>
+      </c>
+      <c r="B341" t="s">
         <v>927</v>
       </c>
-      <c r="B341" t="s">
+      <c r="C341" t="s">
         <v>928</v>
-      </c>
-      <c r="C341" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -12283,18 +12265,18 @@
         <v>987</v>
       </c>
       <c r="C361" t="s">
-        <v>988</v>
+        <v>282</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>988</v>
+      </c>
+      <c r="B362" t="s">
         <v>989</v>
       </c>
-      <c r="B362" t="s">
+      <c r="C362" t="s">
         <v>990</v>
-      </c>
-      <c r="C362" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -12302,21 +12284,21 @@
         <v>991</v>
       </c>
       <c r="B363" t="s">
-        <v>992</v>
+        <v>38</v>
       </c>
       <c r="C363" t="s">
-        <v>993</v>
+        <v>39</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
+        <v>992</v>
+      </c>
+      <c r="B364" t="s">
+        <v>993</v>
+      </c>
+      <c r="C364" t="s">
         <v>994</v>
-      </c>
-      <c r="B364" t="s">
-        <v>38</v>
-      </c>
-      <c r="C364" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -12324,21 +12306,21 @@
         <v>995</v>
       </c>
       <c r="B365" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C365" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>996</v>
+      </c>
+      <c r="B366" t="s">
+        <v>997</v>
+      </c>
+      <c r="C366" t="s">
         <v>998</v>
-      </c>
-      <c r="B366" t="s">
-        <v>996</v>
-      </c>
-      <c r="C366" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -12632,29 +12614,29 @@
         <v>1077</v>
       </c>
       <c r="B393" t="s">
-        <v>1078</v>
+        <v>987</v>
       </c>
       <c r="C393" t="s">
-        <v>1079</v>
+        <v>282</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B394" t="s">
-        <v>990</v>
+        <v>203</v>
       </c>
       <c r="C394" t="s">
-        <v>282</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B395" t="s">
         <v>1081</v>
-      </c>
-      <c r="B395" t="s">
-        <v>203</v>
       </c>
       <c r="C395" t="s">
         <v>1082</v>
@@ -12874,18 +12856,18 @@
         <v>1140</v>
       </c>
       <c r="B415" t="s">
+        <v>634</v>
+      </c>
+      <c r="C415" t="s">
         <v>1141</v>
-      </c>
-      <c r="C415" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B416" t="s">
         <v>1143</v>
-      </c>
-      <c r="B416" t="s">
-        <v>634</v>
       </c>
       <c r="C416" t="s">
         <v>1144</v>
@@ -12972,7 +12954,7 @@
       <c r="A424" t="s">
         <v>1166</v>
       </c>
-      <c r="B424" t="s">
+      <c r="B424" s="1" t="s">
         <v>1167</v>
       </c>
       <c r="C424" t="s">
@@ -12983,7 +12965,7 @@
       <c r="A425" t="s">
         <v>1169</v>
       </c>
-      <c r="B425" s="1" t="s">
+      <c r="B425" t="s">
         <v>1170</v>
       </c>
       <c r="C425" t="s">
@@ -13104,7 +13086,7 @@
       <c r="A436" t="s">
         <v>1202</v>
       </c>
-      <c r="B436" t="s">
+      <c r="B436" s="1" t="s">
         <v>1203</v>
       </c>
       <c r="C436" t="s">
@@ -13115,7 +13097,7 @@
       <c r="A437" t="s">
         <v>1205</v>
       </c>
-      <c r="B437" s="1" t="s">
+      <c r="B437" t="s">
         <v>1206</v>
       </c>
       <c r="C437" t="s">
@@ -13192,7 +13174,7 @@
       <c r="A444" t="s">
         <v>1226</v>
       </c>
-      <c r="B444" t="s">
+      <c r="B444" s="1" t="s">
         <v>1227</v>
       </c>
       <c r="C444" t="s">
@@ -13203,7 +13185,7 @@
       <c r="A445" t="s">
         <v>1229</v>
       </c>
-      <c r="B445" s="1" t="s">
+      <c r="B445" t="s">
         <v>1230</v>
       </c>
       <c r="C445" t="s">
@@ -13401,7 +13383,7 @@
       <c r="A463" t="s">
         <v>1283</v>
       </c>
-      <c r="B463" t="s">
+      <c r="B463" s="1" t="s">
         <v>1284</v>
       </c>
       <c r="C463" t="s">
@@ -13423,7 +13405,7 @@
       <c r="A465" t="s">
         <v>1289</v>
       </c>
-      <c r="B465" s="1" t="s">
+      <c r="B465" t="s">
         <v>1290</v>
       </c>
       <c r="C465" t="s">
@@ -13544,7 +13526,7 @@
       <c r="A476" t="s">
         <v>1322</v>
       </c>
-      <c r="B476" t="s">
+      <c r="B476" s="1" t="s">
         <v>1323</v>
       </c>
       <c r="C476" t="s">
@@ -13566,7 +13548,7 @@
       <c r="A478" t="s">
         <v>1328</v>
       </c>
-      <c r="B478" s="1" t="s">
+      <c r="B478" t="s">
         <v>1329</v>
       </c>
       <c r="C478" t="s">
@@ -13586,24 +13568,24 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B480" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C480" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B481" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C481" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -13622,32 +13604,32 @@
         <v>1344</v>
       </c>
       <c r="B483" t="s">
-        <v>1345</v>
+        <v>987</v>
       </c>
       <c r="C483" t="s">
-        <v>1346</v>
+        <v>282</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C484" t="s">
         <v>1347</v>
-      </c>
-      <c r="B484" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C484" t="s">
-        <v>1349</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C485" t="s">
         <v>1350</v>
-      </c>
-      <c r="B485" t="s">
-        <v>990</v>
-      </c>
-      <c r="C485" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -14219,48 +14201,48 @@
         <v>1505</v>
       </c>
       <c r="C537" t="s">
-        <v>1506</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B538" t="s">
         <v>1507</v>
       </c>
-      <c r="B538" t="s">
+      <c r="C538" t="s">
         <v>1508</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C539" t="s">
         <v>1510</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1511</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B540" t="s">
         <v>1512</v>
       </c>
-      <c r="B540" t="s">
+      <c r="C540" t="s">
         <v>1513</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1514</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B541" t="s">
         <v>1515</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1499</v>
       </c>
       <c r="C541" t="s">
         <v>1516</v>
@@ -14689,29 +14671,29 @@
         <v>1631</v>
       </c>
       <c r="B580" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C580" t="s">
         <v>1632</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B581" t="s">
         <v>1634</v>
       </c>
-      <c r="B581" t="s">
+      <c r="C581" t="s">
         <v>1635</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B582" t="s">
         <v>1637</v>
-      </c>
-      <c r="B582" t="s">
-        <v>1499</v>
       </c>
       <c r="C582" t="s">
         <v>1638</v>
@@ -15165,29 +15147,29 @@
         <v>1760</v>
       </c>
       <c r="C623" t="s">
-        <v>1761</v>
+        <v>614</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B624" t="s">
         <v>1762</v>
       </c>
-      <c r="B624" t="s">
+      <c r="C624" t="s">
         <v>1763</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B625" t="s">
         <v>1765</v>
       </c>
-      <c r="B625" t="s">
+      <c r="C625" t="s">
         <v>1766</v>
-      </c>
-      <c r="C625" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -15583,29 +15565,29 @@
         <v>1873</v>
       </c>
       <c r="C661" t="s">
-        <v>1874</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B662" t="s">
         <v>1875</v>
       </c>
-      <c r="B662" t="s">
+      <c r="C662" t="s">
         <v>1876</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B663" t="s">
         <v>1878</v>
       </c>
-      <c r="B663" t="s">
+      <c r="C663" t="s">
         <v>1879</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -15803,29 +15785,29 @@
         <v>1932</v>
       </c>
       <c r="C681" t="s">
-        <v>1933</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B682" t="s">
         <v>1934</v>
       </c>
-      <c r="B682" t="s">
+      <c r="C682" t="s">
         <v>1935</v>
-      </c>
-      <c r="C682" t="s">
-        <v>1936</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B683" t="s">
         <v>1937</v>
       </c>
-      <c r="B683" t="s">
+      <c r="C683" t="s">
         <v>1938</v>
-      </c>
-      <c r="C683" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -16595,29 +16577,29 @@
         <v>2147</v>
       </c>
       <c r="C753" t="s">
-        <v>2148</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B754" t="s">
         <v>2149</v>
       </c>
-      <c r="B754" t="s">
+      <c r="C754" t="s">
         <v>2150</v>
-      </c>
-      <c r="C754" t="s">
-        <v>2151</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B755" t="s">
         <v>2152</v>
       </c>
-      <c r="B755" t="s">
+      <c r="C755" t="s">
         <v>2153</v>
-      </c>
-      <c r="C755" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.25">
@@ -16683,29 +16665,29 @@
         <v>2170</v>
       </c>
       <c r="C761" t="s">
-        <v>2171</v>
+        <v>294</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B762" t="s">
         <v>2172</v>
       </c>
-      <c r="B762" t="s">
+      <c r="C762" t="s">
         <v>2173</v>
-      </c>
-      <c r="C762" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B763" t="s">
         <v>2175</v>
       </c>
-      <c r="B763" t="s">
+      <c r="C763" t="s">
         <v>2176</v>
-      </c>
-      <c r="C763" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.25">
@@ -16716,29 +16698,29 @@
         <v>2178</v>
       </c>
       <c r="C764" t="s">
-        <v>2179</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B765" t="s">
         <v>2180</v>
       </c>
-      <c r="B765" t="s">
+      <c r="C765" t="s">
         <v>2181</v>
-      </c>
-      <c r="C765" t="s">
-        <v>2182</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B766" t="s">
         <v>2183</v>
       </c>
-      <c r="B766" t="s">
+      <c r="C766" t="s">
         <v>2184</v>
-      </c>
-      <c r="C766" t="s">
-        <v>1525</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.25">
@@ -16848,29 +16830,29 @@
         <v>2213</v>
       </c>
       <c r="C776" t="s">
-        <v>2214</v>
+        <v>497</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B777" t="s">
         <v>2215</v>
       </c>
-      <c r="B777" t="s">
+      <c r="C777" t="s">
         <v>2216</v>
-      </c>
-      <c r="C777" t="s">
-        <v>2217</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B778" t="s">
         <v>2218</v>
       </c>
-      <c r="B778" t="s">
+      <c r="C778" t="s">
         <v>2219</v>
-      </c>
-      <c r="C778" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.25">
@@ -17739,29 +17721,29 @@
         <v>2455</v>
       </c>
       <c r="C857" t="s">
-        <v>2456</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B858" t="s">
         <v>2457</v>
       </c>
-      <c r="B858" t="s">
+      <c r="C858" t="s">
         <v>2458</v>
-      </c>
-      <c r="C858" t="s">
-        <v>2459</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B859" t="s">
         <v>2460</v>
       </c>
-      <c r="B859" t="s">
+      <c r="C859" t="s">
         <v>2461</v>
-      </c>
-      <c r="C859" t="s">
-        <v>2444</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.25">
@@ -18334,28 +18316,6 @@
       </c>
       <c r="C911" t="s">
         <v>2617</v>
-      </c>
-    </row>
-    <row r="912" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A912" t="s">
-        <v>2618</v>
-      </c>
-      <c r="B912" t="s">
-        <v>2619</v>
-      </c>
-      <c r="C912" t="s">
-        <v>2620</v>
-      </c>
-    </row>
-    <row r="913" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A913" t="s">
-        <v>2621</v>
-      </c>
-      <c r="B913" t="s">
-        <v>2622</v>
-      </c>
-      <c r="C913" t="s">
-        <v>2623</v>
       </c>
     </row>
   </sheetData>

--- a/add-in-ids/add-ins-using-exchange-tokens.xlsx
+++ b/add-in-ids/add-ins-using-exchange-tokens.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28717"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9BDEF2-8F23-4ECC-BD34-7BD727B64A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEC815D-DD99-44A2-8C08-999040041229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19395" yWindow="465" windowWidth="18180" windowHeight="14130" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
   </bookViews>
   <sheets>
     <sheet name="Add-ins list" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="2619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2726" uniqueCount="2616">
   <si>
     <t>AssetID</t>
   </si>
@@ -6709,15 +6709,6 @@
   </si>
   <si>
     <t>Awardco</t>
-  </si>
-  <si>
-    <t>wa200004958</t>
-  </si>
-  <si>
-    <t>bb2dab9e-522f-4e44-a001-2457d335e721</t>
-  </si>
-  <si>
-    <t>Showpad for Outlook</t>
   </si>
   <si>
     <t>wa200004960</t>
@@ -7972,8 +7963,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C911" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:C911" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C910" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:C910" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{39B649A1-0CDF-46AA-A276-6F4F89255D96}" name="AssetID"/>
     <tableColumn id="2" xr3:uid="{C79A1EFF-47FF-488B-A562-E9848648C952}" name="AppId"/>
@@ -8300,7 +8291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3293B4AA-89CE-4E6A-9112-DA5B905DDA88}">
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -8314,7 +8305,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2618</v>
+        <v>2615</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -17710,18 +17701,18 @@
         <v>2452</v>
       </c>
       <c r="C856" t="s">
-        <v>2453</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B857" t="s">
         <v>2454</v>
       </c>
-      <c r="B857" t="s">
+      <c r="C857" t="s">
         <v>2455</v>
-      </c>
-      <c r="C857" t="s">
-        <v>2438</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.25">
@@ -18305,17 +18296,6 @@
       </c>
       <c r="C910" t="s">
         <v>2614</v>
-      </c>
-    </row>
-    <row r="911" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A911" t="s">
-        <v>2615</v>
-      </c>
-      <c r="B911" t="s">
-        <v>2616</v>
-      </c>
-      <c r="C911" t="s">
-        <v>2617</v>
       </c>
     </row>
   </sheetData>

--- a/add-in-ids/add-ins-using-exchange-tokens.xlsx
+++ b/add-in-ids/add-ins-using-exchange-tokens.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28717"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4871A9-D8C6-4631-A5EA-C89F1411410B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98FDA49-AD15-4DD6-94FA-078686B5ACBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="1350" windowWidth="18180" windowHeight="14130" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
+    <workbookView xWindow="20175" yWindow="885" windowWidth="15210" windowHeight="14160" xr2:uid="{8FF931F1-CAD9-4954-9038-88E82260DB46}"/>
   </bookViews>
   <sheets>
     <sheet name="Add-ins list" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="2371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="2368">
   <si>
     <t>AssetID</t>
   </si>
@@ -5848,15 +5848,6 @@
   </si>
   <si>
     <t>Visavid</t>
-  </si>
-  <si>
-    <t>wa200004729</t>
-  </si>
-  <si>
-    <t>b6b03dd8-824e-44b1-95dd-c86590b3dc85</t>
-  </si>
-  <si>
-    <t>Culture Cloud</t>
   </si>
   <si>
     <t>wa200004742</t>
@@ -7150,7 +7141,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7244,8 +7235,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C827" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:C827" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}" name="Table1" displayName="Table1" ref="A1:C826" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:C826" xr:uid="{CD6B8178-56C6-442C-A6BF-7C2D1F869861}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{39B649A1-0CDF-46AA-A276-6F4F89255D96}" name="AssetID"/>
     <tableColumn id="2" xr3:uid="{C79A1EFF-47FF-488B-A562-E9848648C952}" name="AppId"/>
@@ -7572,27 +7563,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3293B4AA-89CE-4E6A-9112-DA5B905DDA88}">
-  <dimension ref="A1:C827"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C826"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="40.25" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -7601,7 +7592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -7610,7 +7601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -7619,7 +7610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -7628,7 +7619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -7639,7 +7630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -7650,7 +7641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -7661,7 +7652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
@@ -7672,7 +7663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -7683,7 +7674,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
@@ -7694,7 +7685,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -7705,7 +7696,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
@@ -7716,7 +7707,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
@@ -7727,7 +7718,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
@@ -7738,7 +7729,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
@@ -7749,7 +7740,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="3" t="s">
         <v>43</v>
       </c>
@@ -7760,7 +7751,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
         <v>46</v>
       </c>
@@ -7771,7 +7762,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
         <v>49</v>
       </c>
@@ -7782,7 +7773,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
         <v>52</v>
       </c>
@@ -7793,7 +7784,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
         <v>55</v>
       </c>
@@ -7804,7 +7795,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
         <v>58</v>
       </c>
@@ -7815,7 +7806,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
         <v>61</v>
       </c>
@@ -7826,7 +7817,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
         <v>64</v>
       </c>
@@ -7837,7 +7828,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
         <v>67</v>
       </c>
@@ -7848,7 +7839,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
         <v>70</v>
       </c>
@@ -7859,7 +7850,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
         <v>73</v>
       </c>
@@ -7870,7 +7861,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
         <v>76</v>
       </c>
@@ -7881,7 +7872,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
         <v>79</v>
       </c>
@@ -7892,7 +7883,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
         <v>82</v>
       </c>
@@ -7903,7 +7894,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
         <v>85</v>
       </c>
@@ -7914,7 +7905,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
         <v>88</v>
       </c>
@@ -7925,7 +7916,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" s="3" t="s">
         <v>91</v>
       </c>
@@ -7936,7 +7927,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
         <v>94</v>
       </c>
@@ -7947,7 +7938,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" s="3" t="s">
         <v>97</v>
       </c>
@@ -7958,7 +7949,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
         <v>100</v>
       </c>
@@ -7969,7 +7960,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
         <v>103</v>
       </c>
@@ -7980,7 +7971,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
         <v>106</v>
       </c>
@@ -7991,7 +7982,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
         <v>109</v>
       </c>
@@ -8002,7 +7993,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
         <v>112</v>
       </c>
@@ -8013,7 +8004,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" s="3" t="s">
         <v>115</v>
       </c>
@@ -8024,7 +8015,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
         <v>118</v>
       </c>
@@ -8035,7 +8026,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" s="3" t="s">
         <v>121</v>
       </c>
@@ -8046,7 +8037,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
         <v>124</v>
       </c>
@@ -8057,7 +8048,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" s="3" t="s">
         <v>127</v>
       </c>
@@ -8068,7 +8059,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
         <v>130</v>
       </c>
@@ -8079,7 +8070,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" s="3" t="s">
         <v>133</v>
       </c>
@@ -8090,7 +8081,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
         <v>136</v>
       </c>
@@ -8101,7 +8092,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" s="3" t="s">
         <v>139</v>
       </c>
@@ -8112,7 +8103,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
         <v>142</v>
       </c>
@@ -8123,7 +8114,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" s="3" t="s">
         <v>145</v>
       </c>
@@ -8134,7 +8125,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
         <v>148</v>
       </c>
@@ -8145,7 +8136,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" s="3" t="s">
         <v>151</v>
       </c>
@@ -8156,7 +8147,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
         <v>154</v>
       </c>
@@ -8167,7 +8158,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" s="3" t="s">
         <v>157</v>
       </c>
@@ -8178,7 +8169,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" s="2" t="s">
         <v>160</v>
       </c>
@@ -8189,7 +8180,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" s="3" t="s">
         <v>163</v>
       </c>
@@ -8200,7 +8191,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
         <v>166</v>
       </c>
@@ -8211,7 +8202,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
         <v>169</v>
       </c>
@@ -8222,7 +8213,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" s="2" t="s">
         <v>172</v>
       </c>
@@ -8233,7 +8224,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" s="3" t="s">
         <v>175</v>
       </c>
@@ -8244,7 +8235,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62" s="2" t="s">
         <v>178</v>
       </c>
@@ -8255,7 +8246,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" s="3" t="s">
         <v>181</v>
       </c>
@@ -8266,7 +8257,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" s="2" t="s">
         <v>184</v>
       </c>
@@ -8277,7 +8268,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" s="3" t="s">
         <v>187</v>
       </c>
@@ -8288,7 +8279,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66" s="2" t="s">
         <v>190</v>
       </c>
@@ -8299,7 +8290,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67" s="3" t="s">
         <v>193</v>
       </c>
@@ -8310,7 +8301,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68" s="2" t="s">
         <v>196</v>
       </c>
@@ -8321,7 +8312,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69" s="3" t="s">
         <v>199</v>
       </c>
@@ -8332,7 +8323,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70" s="2" t="s">
         <v>202</v>
       </c>
@@ -8343,7 +8334,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71" s="3" t="s">
         <v>205</v>
       </c>
@@ -8354,7 +8345,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72" s="2" t="s">
         <v>208</v>
       </c>
@@ -8365,7 +8356,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73" s="3" t="s">
         <v>211</v>
       </c>
@@ -8376,7 +8367,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74" s="2" t="s">
         <v>214</v>
       </c>
@@ -8387,7 +8378,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75" s="3" t="s">
         <v>217</v>
       </c>
@@ -8398,7 +8389,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
         <v>220</v>
       </c>
@@ -8409,7 +8400,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77" s="3" t="s">
         <v>223</v>
       </c>
@@ -8420,7 +8411,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
         <v>226</v>
       </c>
@@ -8431,7 +8422,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79" s="3" t="s">
         <v>229</v>
       </c>
@@ -8442,7 +8433,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80" s="2" t="s">
         <v>232</v>
       </c>
@@ -8453,7 +8444,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="A81" s="3" t="s">
         <v>235</v>
       </c>
@@ -8464,7 +8455,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
         <v>238</v>
       </c>
@@ -8475,7 +8466,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3">
       <c r="A83" s="3" t="s">
         <v>241</v>
       </c>
@@ -8486,7 +8477,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
         <v>244</v>
       </c>
@@ -8497,7 +8488,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="A85" s="3" t="s">
         <v>247</v>
       </c>
@@ -8508,7 +8499,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86" s="2" t="s">
         <v>250</v>
       </c>
@@ -8519,7 +8510,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3">
       <c r="A87" s="3" t="s">
         <v>253</v>
       </c>
@@ -8530,7 +8521,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
         <v>256</v>
       </c>
@@ -8541,7 +8532,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="A89" s="3" t="s">
         <v>259</v>
       </c>
@@ -8552,7 +8543,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
         <v>262</v>
       </c>
@@ -8563,7 +8554,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3">
       <c r="A91" s="3" t="s">
         <v>265</v>
       </c>
@@ -8574,7 +8565,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="A92" s="2" t="s">
         <v>268</v>
       </c>
@@ -8585,7 +8576,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="A93" s="3" t="s">
         <v>271</v>
       </c>
@@ -8596,7 +8587,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="A94" s="2" t="s">
         <v>274</v>
       </c>
@@ -8607,7 +8598,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3">
       <c r="A95" s="3" t="s">
         <v>277</v>
       </c>
@@ -8618,7 +8609,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3">
       <c r="A96" s="2" t="s">
         <v>280</v>
       </c>
@@ -8629,7 +8620,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3">
       <c r="A97" s="3" t="s">
         <v>283</v>
       </c>
@@ -8640,7 +8631,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3">
       <c r="A98" s="2" t="s">
         <v>286</v>
       </c>
@@ -8651,7 +8642,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3">
       <c r="A99" s="3" t="s">
         <v>289</v>
       </c>
@@ -8662,7 +8653,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3">
       <c r="A100" s="2" t="s">
         <v>292</v>
       </c>
@@ -8673,7 +8664,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3">
       <c r="A101" s="3" t="s">
         <v>295</v>
       </c>
@@ -8684,7 +8675,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3">
       <c r="A102" s="2" t="s">
         <v>298</v>
       </c>
@@ -8695,7 +8686,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3">
       <c r="A103" s="3" t="s">
         <v>301</v>
       </c>
@@ -8706,7 +8697,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3">
       <c r="A104" s="2" t="s">
         <v>304</v>
       </c>
@@ -8717,7 +8708,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3">
       <c r="A105" s="3" t="s">
         <v>307</v>
       </c>
@@ -8728,7 +8719,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3">
       <c r="A106" s="2" t="s">
         <v>310</v>
       </c>
@@ -8739,7 +8730,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3">
       <c r="A107" s="3" t="s">
         <v>313</v>
       </c>
@@ -8750,7 +8741,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3">
       <c r="A108" s="2" t="s">
         <v>316</v>
       </c>
@@ -8761,7 +8752,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3">
       <c r="A109" s="3" t="s">
         <v>319</v>
       </c>
@@ -8772,7 +8763,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3">
       <c r="A110" s="2" t="s">
         <v>322</v>
       </c>
@@ -8783,7 +8774,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3">
       <c r="A111" s="3" t="s">
         <v>325</v>
       </c>
@@ -8794,7 +8785,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3">
       <c r="A112" s="2" t="s">
         <v>328</v>
       </c>
@@ -8805,7 +8796,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3">
       <c r="A113" s="3" t="s">
         <v>331</v>
       </c>
@@ -8816,7 +8807,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3">
       <c r="A114" s="2" t="s">
         <v>334</v>
       </c>
@@ -8827,7 +8818,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3">
       <c r="A115" s="3" t="s">
         <v>337</v>
       </c>
@@ -8838,7 +8829,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3">
       <c r="A116" s="2" t="s">
         <v>340</v>
       </c>
@@ -8849,7 +8840,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3">
       <c r="A117" s="3" t="s">
         <v>343</v>
       </c>
@@ -8860,7 +8851,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3">
       <c r="A118" s="2" t="s">
         <v>346</v>
       </c>
@@ -8871,7 +8862,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3">
       <c r="A119" s="3" t="s">
         <v>349</v>
       </c>
@@ -8882,7 +8873,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3">
       <c r="A120" s="2" t="s">
         <v>352</v>
       </c>
@@ -8893,7 +8884,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3">
       <c r="A121" s="3" t="s">
         <v>355</v>
       </c>
@@ -8904,7 +8895,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3">
       <c r="A122" s="2" t="s">
         <v>358</v>
       </c>
@@ -8915,7 +8906,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3">
       <c r="A123" s="3" t="s">
         <v>361</v>
       </c>
@@ -8926,7 +8917,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3">
       <c r="A124" s="2" t="s">
         <v>364</v>
       </c>
@@ -8937,7 +8928,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3">
       <c r="A125" s="3" t="s">
         <v>367</v>
       </c>
@@ -8948,7 +8939,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3">
       <c r="A126" s="2" t="s">
         <v>370</v>
       </c>
@@ -8959,7 +8950,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3">
       <c r="A127" s="3" t="s">
         <v>373</v>
       </c>
@@ -8970,7 +8961,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3">
       <c r="A128" s="2" t="s">
         <v>376</v>
       </c>
@@ -8981,7 +8972,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3">
       <c r="A129" s="3" t="s">
         <v>379</v>
       </c>
@@ -8992,7 +8983,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3">
       <c r="A130" s="2" t="s">
         <v>382</v>
       </c>
@@ -9003,7 +8994,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3">
       <c r="A131" s="3" t="s">
         <v>385</v>
       </c>
@@ -9014,7 +9005,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3">
       <c r="A132" s="2" t="s">
         <v>388</v>
       </c>
@@ -9025,7 +9016,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3">
       <c r="A133" s="3" t="s">
         <v>391</v>
       </c>
@@ -9036,7 +9027,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3">
       <c r="A134" s="2" t="s">
         <v>394</v>
       </c>
@@ -9047,7 +9038,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3">
       <c r="A135" s="3" t="s">
         <v>397</v>
       </c>
@@ -9058,7 +9049,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3">
       <c r="A136" s="2" t="s">
         <v>400</v>
       </c>
@@ -9069,7 +9060,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3">
       <c r="A137" s="3" t="s">
         <v>403</v>
       </c>
@@ -9080,7 +9071,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3">
       <c r="A138" s="2" t="s">
         <v>406</v>
       </c>
@@ -9091,7 +9082,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3">
       <c r="A139" s="3" t="s">
         <v>409</v>
       </c>
@@ -9102,7 +9093,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3">
       <c r="A140" s="2" t="s">
         <v>412</v>
       </c>
@@ -9113,7 +9104,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3">
       <c r="A141" s="3" t="s">
         <v>415</v>
       </c>
@@ -9124,7 +9115,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3">
       <c r="A142" s="2" t="s">
         <v>418</v>
       </c>
@@ -9135,7 +9126,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3">
       <c r="A143" s="3" t="s">
         <v>421</v>
       </c>
@@ -9146,7 +9137,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3">
       <c r="A144" s="2" t="s">
         <v>424</v>
       </c>
@@ -9157,7 +9148,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3">
       <c r="A145" s="3" t="s">
         <v>427</v>
       </c>
@@ -9168,7 +9159,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3">
       <c r="A146" s="2" t="s">
         <v>430</v>
       </c>
@@ -9179,7 +9170,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3">
       <c r="A147" s="3" t="s">
         <v>433</v>
       </c>
@@ -9190,7 +9181,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3">
       <c r="A148" s="2" t="s">
         <v>436</v>
       </c>
@@ -9201,7 +9192,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3">
       <c r="A149" s="3" t="s">
         <v>439</v>
       </c>
@@ -9212,7 +9203,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3">
       <c r="A150" s="2" t="s">
         <v>442</v>
       </c>
@@ -9223,7 +9214,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3">
       <c r="A151" s="3" t="s">
         <v>445</v>
       </c>
@@ -9234,7 +9225,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3">
       <c r="A152" s="2" t="s">
         <v>448</v>
       </c>
@@ -9245,7 +9236,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3">
       <c r="A153" s="3" t="s">
         <v>451</v>
       </c>
@@ -9256,7 +9247,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3">
       <c r="A154" s="2" t="s">
         <v>454</v>
       </c>
@@ -9267,7 +9258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3">
       <c r="A155" s="3" t="s">
         <v>457</v>
       </c>
@@ -9278,7 +9269,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3">
       <c r="A156" s="2" t="s">
         <v>460</v>
       </c>
@@ -9289,7 +9280,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3">
       <c r="A157" s="3" t="s">
         <v>463</v>
       </c>
@@ -9300,7 +9291,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3">
       <c r="A158" s="2" t="s">
         <v>466</v>
       </c>
@@ -9311,7 +9302,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3">
       <c r="A159" s="3" t="s">
         <v>469</v>
       </c>
@@ -9322,7 +9313,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3">
       <c r="A160" s="2" t="s">
         <v>472</v>
       </c>
@@ -9333,7 +9324,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3">
       <c r="A161" s="3" t="s">
         <v>475</v>
       </c>
@@ -9344,7 +9335,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3">
       <c r="A162" s="2" t="s">
         <v>478</v>
       </c>
@@ -9355,7 +9346,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3">
       <c r="A163" s="3" t="s">
         <v>481</v>
       </c>
@@ -9366,7 +9357,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3">
       <c r="A164" s="2" t="s">
         <v>484</v>
       </c>
@@ -9377,7 +9368,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3">
       <c r="A165" s="3" t="s">
         <v>487</v>
       </c>
@@ -9388,7 +9379,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3">
       <c r="A166" s="2" t="s">
         <v>490</v>
       </c>
@@ -9399,7 +9390,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3">
       <c r="A167" s="3" t="s">
         <v>493</v>
       </c>
@@ -9410,7 +9401,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3">
       <c r="A168" s="2" t="s">
         <v>496</v>
       </c>
@@ -9421,7 +9412,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3">
       <c r="A169" s="3" t="s">
         <v>499</v>
       </c>
@@ -9432,7 +9423,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3">
       <c r="A170" s="2" t="s">
         <v>502</v>
       </c>
@@ -9443,7 +9434,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3">
       <c r="A171" s="3" t="s">
         <v>505</v>
       </c>
@@ -9454,7 +9445,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3">
       <c r="A172" s="2" t="s">
         <v>508</v>
       </c>
@@ -9465,7 +9456,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3">
       <c r="A173" s="3" t="s">
         <v>511</v>
       </c>
@@ -9476,7 +9467,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3">
       <c r="A174" s="2" t="s">
         <v>514</v>
       </c>
@@ -9487,7 +9478,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3">
       <c r="A175" s="3" t="s">
         <v>517</v>
       </c>
@@ -9498,7 +9489,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3">
       <c r="A176" s="2" t="s">
         <v>520</v>
       </c>
@@ -9509,7 +9500,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3">
       <c r="A177" s="3" t="s">
         <v>523</v>
       </c>
@@ -9520,7 +9511,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3">
       <c r="A178" s="2" t="s">
         <v>526</v>
       </c>
@@ -9531,7 +9522,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3">
       <c r="A179" s="3" t="s">
         <v>529</v>
       </c>
@@ -9542,7 +9533,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3">
       <c r="A180" s="2" t="s">
         <v>532</v>
       </c>
@@ -9553,7 +9544,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3">
       <c r="A181" s="3" t="s">
         <v>535</v>
       </c>
@@ -9564,7 +9555,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3">
       <c r="A182" s="2" t="s">
         <v>538</v>
       </c>
@@ -9575,7 +9566,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3">
       <c r="A183" s="3" t="s">
         <v>541</v>
       </c>
@@ -9586,7 +9577,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3">
       <c r="A184" s="2" t="s">
         <v>544</v>
       </c>
@@ -9597,7 +9588,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3">
       <c r="A185" s="3" t="s">
         <v>547</v>
       </c>
@@ -9608,7 +9599,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3">
       <c r="A186" s="2" t="s">
         <v>550</v>
       </c>
@@ -9619,7 +9610,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3">
       <c r="A187" s="3" t="s">
         <v>553</v>
       </c>
@@ -9630,7 +9621,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3">
       <c r="A188" s="2" t="s">
         <v>556</v>
       </c>
@@ -9641,7 +9632,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3">
       <c r="A189" s="3" t="s">
         <v>559</v>
       </c>
@@ -9652,7 +9643,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3">
       <c r="A190" s="2" t="s">
         <v>562</v>
       </c>
@@ -9663,7 +9654,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3">
       <c r="A191" s="3" t="s">
         <v>565</v>
       </c>
@@ -9674,7 +9665,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3">
       <c r="A192" s="2" t="s">
         <v>568</v>
       </c>
@@ -9685,7 +9676,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3">
       <c r="A193" s="3" t="s">
         <v>571</v>
       </c>
@@ -9696,7 +9687,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3">
       <c r="A194" s="2" t="s">
         <v>574</v>
       </c>
@@ -9707,7 +9698,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3">
       <c r="A195" s="3" t="s">
         <v>577</v>
       </c>
@@ -9718,7 +9709,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3">
       <c r="A196" s="2" t="s">
         <v>580</v>
       </c>
@@ -9729,7 +9720,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3">
       <c r="A197" s="3" t="s">
         <v>583</v>
       </c>
@@ -9740,7 +9731,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3">
       <c r="A198" s="2" t="s">
         <v>586</v>
       </c>
@@ -9751,7 +9742,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3">
       <c r="A199" s="3" t="s">
         <v>589</v>
       </c>
@@ -9762,7 +9753,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3">
       <c r="A200" s="2" t="s">
         <v>592</v>
       </c>
@@ -9773,7 +9764,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3">
       <c r="A201" s="3" t="s">
         <v>595</v>
       </c>
@@ -9784,7 +9775,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3">
       <c r="A202" s="2" t="s">
         <v>598</v>
       </c>
@@ -9795,7 +9786,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3">
       <c r="A203" s="3" t="s">
         <v>601</v>
       </c>
@@ -9806,7 +9797,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3">
       <c r="A204" s="2" t="s">
         <v>604</v>
       </c>
@@ -9817,7 +9808,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3">
       <c r="A205" s="3" t="s">
         <v>607</v>
       </c>
@@ -9828,7 +9819,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3">
       <c r="A206" s="2" t="s">
         <v>610</v>
       </c>
@@ -9839,7 +9830,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3">
       <c r="A207" s="3" t="s">
         <v>613</v>
       </c>
@@ -9850,7 +9841,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3">
       <c r="A208" s="2" t="s">
         <v>616</v>
       </c>
@@ -9861,7 +9852,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3">
       <c r="A209" s="3" t="s">
         <v>619</v>
       </c>
@@ -9872,7 +9863,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3">
       <c r="A210" s="2" t="s">
         <v>622</v>
       </c>
@@ -9883,7 +9874,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3">
       <c r="A211" s="3" t="s">
         <v>625</v>
       </c>
@@ -9894,7 +9885,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3">
       <c r="A212" s="2" t="s">
         <v>628</v>
       </c>
@@ -9905,7 +9896,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3">
       <c r="A213" s="3" t="s">
         <v>631</v>
       </c>
@@ -9916,7 +9907,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3">
       <c r="A214" s="2" t="s">
         <v>634</v>
       </c>
@@ -9927,7 +9918,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3">
       <c r="A215" s="3" t="s">
         <v>637</v>
       </c>
@@ -9938,7 +9929,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3">
       <c r="A216" s="2" t="s">
         <v>640</v>
       </c>
@@ -9949,7 +9940,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3">
       <c r="A217" s="3" t="s">
         <v>643</v>
       </c>
@@ -9960,7 +9951,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3">
       <c r="A218" s="2" t="s">
         <v>646</v>
       </c>
@@ -9971,7 +9962,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3">
       <c r="A219" s="3" t="s">
         <v>649</v>
       </c>
@@ -9982,7 +9973,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3">
       <c r="A220" s="2" t="s">
         <v>652</v>
       </c>
@@ -9993,7 +9984,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3">
       <c r="A221" s="3" t="s">
         <v>655</v>
       </c>
@@ -10004,7 +9995,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3">
       <c r="A222" s="2" t="s">
         <v>658</v>
       </c>
@@ -10015,7 +10006,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3">
       <c r="A223" s="3" t="s">
         <v>661</v>
       </c>
@@ -10026,7 +10017,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3">
       <c r="A224" s="2" t="s">
         <v>664</v>
       </c>
@@ -10037,7 +10028,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3">
       <c r="A225" s="3" t="s">
         <v>667</v>
       </c>
@@ -10048,7 +10039,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3">
       <c r="A226" s="2" t="s">
         <v>670</v>
       </c>
@@ -10059,7 +10050,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3">
       <c r="A227" s="3" t="s">
         <v>673</v>
       </c>
@@ -10070,7 +10061,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3">
       <c r="A228" s="2" t="s">
         <v>676</v>
       </c>
@@ -10081,7 +10072,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3">
       <c r="A229" s="3" t="s">
         <v>679</v>
       </c>
@@ -10092,7 +10083,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3">
       <c r="A230" s="2" t="s">
         <v>682</v>
       </c>
@@ -10103,7 +10094,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3">
       <c r="A231" s="3" t="s">
         <v>685</v>
       </c>
@@ -10114,7 +10105,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3">
       <c r="A232" s="2" t="s">
         <v>688</v>
       </c>
@@ -10125,7 +10116,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3">
       <c r="A233" s="3" t="s">
         <v>691</v>
       </c>
@@ -10136,7 +10127,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3">
       <c r="A234" s="2" t="s">
         <v>694</v>
       </c>
@@ -10147,7 +10138,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3">
       <c r="A235" s="3" t="s">
         <v>695</v>
       </c>
@@ -10158,7 +10149,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3">
       <c r="A236" s="2" t="s">
         <v>696</v>
       </c>
@@ -10169,7 +10160,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3">
       <c r="A237" s="3" t="s">
         <v>697</v>
       </c>
@@ -10180,7 +10171,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3">
       <c r="A238" s="2" t="s">
         <v>698</v>
       </c>
@@ -10191,7 +10182,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3">
       <c r="A239" s="3" t="s">
         <v>699</v>
       </c>
@@ -10202,7 +10193,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3">
       <c r="A240" s="2" t="s">
         <v>700</v>
       </c>
@@ -10213,7 +10204,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3">
       <c r="A241" s="3" t="s">
         <v>703</v>
       </c>
@@ -10224,7 +10215,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3">
       <c r="A242" s="2" t="s">
         <v>706</v>
       </c>
@@ -10235,7 +10226,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3">
       <c r="A243" s="3" t="s">
         <v>707</v>
       </c>
@@ -10246,7 +10237,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3">
       <c r="A244" s="2" t="s">
         <v>708</v>
       </c>
@@ -10257,7 +10248,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3">
       <c r="A245" s="3" t="s">
         <v>709</v>
       </c>
@@ -10268,7 +10259,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3">
       <c r="A246" s="2" t="s">
         <v>710</v>
       </c>
@@ -10279,7 +10270,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3">
       <c r="A247" s="3" t="s">
         <v>713</v>
       </c>
@@ -10290,7 +10281,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3">
       <c r="A248" s="2" t="s">
         <v>716</v>
       </c>
@@ -10301,7 +10292,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3">
       <c r="A249" s="3" t="s">
         <v>717</v>
       </c>
@@ -10312,7 +10303,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3">
       <c r="A250" s="2" t="s">
         <v>720</v>
       </c>
@@ -10323,7 +10314,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3">
       <c r="A251" s="3" t="s">
         <v>721</v>
       </c>
@@ -10334,7 +10325,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3">
       <c r="A252" s="2" t="s">
         <v>722</v>
       </c>
@@ -10345,7 +10336,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3">
       <c r="A253" s="3" t="s">
         <v>725</v>
       </c>
@@ -10356,7 +10347,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3">
       <c r="A254" s="2" t="s">
         <v>728</v>
       </c>
@@ -10367,7 +10358,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3">
       <c r="A255" s="3" t="s">
         <v>731</v>
       </c>
@@ -10378,7 +10369,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3">
       <c r="A256" s="2" t="s">
         <v>734</v>
       </c>
@@ -10389,7 +10380,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3">
       <c r="A257" s="3" t="s">
         <v>737</v>
       </c>
@@ -10400,7 +10391,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3">
       <c r="A258" s="2" t="s">
         <v>740</v>
       </c>
@@ -10411,7 +10402,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3">
       <c r="A259" s="3" t="s">
         <v>741</v>
       </c>
@@ -10422,7 +10413,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3">
       <c r="A260" s="2" t="s">
         <v>744</v>
       </c>
@@ -10433,7 +10424,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3">
       <c r="A261" s="3" t="s">
         <v>745</v>
       </c>
@@ -10444,7 +10435,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3">
       <c r="A262" s="2" t="s">
         <v>746</v>
       </c>
@@ -10455,7 +10446,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3">
       <c r="A263" s="3" t="s">
         <v>747</v>
       </c>
@@ -10466,7 +10457,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3">
       <c r="A264" s="2" t="s">
         <v>748</v>
       </c>
@@ -10477,7 +10468,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3">
       <c r="A265" s="3" t="s">
         <v>749</v>
       </c>
@@ -10488,7 +10479,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3">
       <c r="A266" s="2" t="s">
         <v>750</v>
       </c>
@@ -10499,7 +10490,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3">
       <c r="A267" s="3" t="s">
         <v>751</v>
       </c>
@@ -10510,7 +10501,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3">
       <c r="A268" s="2" t="s">
         <v>752</v>
       </c>
@@ -10521,7 +10512,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3">
       <c r="A269" s="3" t="s">
         <v>753</v>
       </c>
@@ -10532,7 +10523,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3">
       <c r="A270" s="2" t="s">
         <v>754</v>
       </c>
@@ -10543,7 +10534,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3">
       <c r="A271" s="3" t="s">
         <v>755</v>
       </c>
@@ -10554,7 +10545,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3">
       <c r="A272" s="2" t="s">
         <v>756</v>
       </c>
@@ -10565,7 +10556,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3">
       <c r="A273" s="3" t="s">
         <v>757</v>
       </c>
@@ -10576,7 +10567,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3">
       <c r="A274" s="2" t="s">
         <v>758</v>
       </c>
@@ -10587,7 +10578,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3">
       <c r="A275" s="3" t="s">
         <v>759</v>
       </c>
@@ -10598,7 +10589,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3">
       <c r="A276" s="2" t="s">
         <v>760</v>
       </c>
@@ -10609,7 +10600,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3">
       <c r="A277" s="3" t="s">
         <v>761</v>
       </c>
@@ -10620,7 +10611,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3">
       <c r="A278" s="2" t="s">
         <v>762</v>
       </c>
@@ -10631,7 +10622,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3">
       <c r="A279" s="3" t="s">
         <v>763</v>
       </c>
@@ -10642,7 +10633,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3">
       <c r="A280" s="2" t="s">
         <v>764</v>
       </c>
@@ -10653,7 +10644,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3">
       <c r="A281" s="3" t="s">
         <v>765</v>
       </c>
@@ -10664,7 +10655,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3">
       <c r="A282" s="2" t="s">
         <v>766</v>
       </c>
@@ -10675,7 +10666,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3">
       <c r="A283" s="3" t="s">
         <v>769</v>
       </c>
@@ -10686,7 +10677,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3">
       <c r="A284" s="2" t="s">
         <v>770</v>
       </c>
@@ -10697,7 +10688,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3">
       <c r="A285" s="3" t="s">
         <v>771</v>
       </c>
@@ -10708,7 +10699,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3">
       <c r="A286" s="2" t="s">
         <v>772</v>
       </c>
@@ -10719,7 +10710,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3">
       <c r="A287" s="3" t="s">
         <v>773</v>
       </c>
@@ -10730,7 +10721,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3">
       <c r="A288" s="2" t="s">
         <v>774</v>
       </c>
@@ -10741,7 +10732,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3">
       <c r="A289" s="3" t="s">
         <v>777</v>
       </c>
@@ -10752,7 +10743,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3">
       <c r="A290" s="2" t="s">
         <v>778</v>
       </c>
@@ -10763,7 +10754,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3">
       <c r="A291" s="3" t="s">
         <v>779</v>
       </c>
@@ -10774,7 +10765,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3">
       <c r="A292" s="2" t="s">
         <v>782</v>
       </c>
@@ -10785,7 +10776,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3">
       <c r="A293" s="3" t="s">
         <v>785</v>
       </c>
@@ -10796,7 +10787,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3">
       <c r="A294" s="2" t="s">
         <v>788</v>
       </c>
@@ -10807,7 +10798,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3">
       <c r="A295" s="3" t="s">
         <v>790</v>
       </c>
@@ -10818,7 +10809,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3">
       <c r="A296" s="2" t="s">
         <v>793</v>
       </c>
@@ -10829,7 +10820,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3">
       <c r="A297" s="3" t="s">
         <v>796</v>
       </c>
@@ -10840,7 +10831,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3">
       <c r="A298" s="2" t="s">
         <v>799</v>
       </c>
@@ -10851,7 +10842,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3">
       <c r="A299" s="3" t="s">
         <v>802</v>
       </c>
@@ -10862,7 +10853,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3">
       <c r="A300" s="2" t="s">
         <v>805</v>
       </c>
@@ -10873,7 +10864,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3">
       <c r="A301" s="3" t="s">
         <v>808</v>
       </c>
@@ -10884,7 +10875,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3">
       <c r="A302" s="2" t="s">
         <v>811</v>
       </c>
@@ -10895,7 +10886,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3">
       <c r="A303" s="3" t="s">
         <v>814</v>
       </c>
@@ -10906,7 +10897,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3">
       <c r="A304" s="2" t="s">
         <v>817</v>
       </c>
@@ -10917,7 +10908,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3">
       <c r="A305" s="3" t="s">
         <v>820</v>
       </c>
@@ -10928,7 +10919,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3">
       <c r="A306" s="2" t="s">
         <v>823</v>
       </c>
@@ -10939,7 +10930,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3">
       <c r="A307" s="3" t="s">
         <v>826</v>
       </c>
@@ -10950,7 +10941,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3">
       <c r="A308" s="2" t="s">
         <v>829</v>
       </c>
@@ -10961,7 +10952,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3">
       <c r="A309" s="3" t="s">
         <v>832</v>
       </c>
@@ -10972,7 +10963,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3">
       <c r="A310" s="2" t="s">
         <v>835</v>
       </c>
@@ -10983,7 +10974,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3">
       <c r="A311" s="3" t="s">
         <v>838</v>
       </c>
@@ -10994,7 +10985,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3">
       <c r="A312" s="2" t="s">
         <v>841</v>
       </c>
@@ -11005,7 +10996,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3">
       <c r="A313" s="3" t="s">
         <v>844</v>
       </c>
@@ -11016,7 +11007,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3">
       <c r="A314" s="2" t="s">
         <v>847</v>
       </c>
@@ -11027,7 +11018,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3">
       <c r="A315" s="3" t="s">
         <v>849</v>
       </c>
@@ -11038,7 +11029,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3">
       <c r="A316" s="2" t="s">
         <v>852</v>
       </c>
@@ -11049,7 +11040,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3">
       <c r="A317" s="3" t="s">
         <v>853</v>
       </c>
@@ -11060,7 +11051,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3">
       <c r="A318" s="2" t="s">
         <v>856</v>
       </c>
@@ -11071,7 +11062,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3">
       <c r="A319" s="3" t="s">
         <v>857</v>
       </c>
@@ -11082,7 +11073,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3">
       <c r="A320" s="2" t="s">
         <v>860</v>
       </c>
@@ -11093,7 +11084,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3">
       <c r="A321" s="3" t="s">
         <v>863</v>
       </c>
@@ -11104,7 +11095,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3">
       <c r="A322" s="2" t="s">
         <v>866</v>
       </c>
@@ -11115,7 +11106,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3">
       <c r="A323" s="3" t="s">
         <v>869</v>
       </c>
@@ -11126,7 +11117,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3">
       <c r="A324" s="2" t="s">
         <v>872</v>
       </c>
@@ -11137,7 +11128,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3">
       <c r="A325" s="3" t="s">
         <v>875</v>
       </c>
@@ -11148,7 +11139,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3">
       <c r="A326" s="2" t="s">
         <v>878</v>
       </c>
@@ -11159,7 +11150,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3">
       <c r="A327" s="3" t="s">
         <v>881</v>
       </c>
@@ -11170,7 +11161,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3">
       <c r="A328" s="2" t="s">
         <v>884</v>
       </c>
@@ -11181,7 +11172,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3">
       <c r="A329" s="3" t="s">
         <v>887</v>
       </c>
@@ -11192,7 +11183,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3">
       <c r="A330" s="2" t="s">
         <v>890</v>
       </c>
@@ -11203,7 +11194,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3">
       <c r="A331" s="3" t="s">
         <v>893</v>
       </c>
@@ -11214,7 +11205,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3">
       <c r="A332" s="2" t="s">
         <v>896</v>
       </c>
@@ -11225,7 +11216,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3">
       <c r="A333" s="3" t="s">
         <v>899</v>
       </c>
@@ -11236,7 +11227,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3">
       <c r="A334" s="2" t="s">
         <v>902</v>
       </c>
@@ -11247,7 +11238,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3">
       <c r="A335" s="3" t="s">
         <v>905</v>
       </c>
@@ -11258,7 +11249,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3">
       <c r="A336" s="2" t="s">
         <v>908</v>
       </c>
@@ -11269,7 +11260,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3">
       <c r="A337" s="3" t="s">
         <v>911</v>
       </c>
@@ -11280,7 +11271,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3">
       <c r="A338" s="2" t="s">
         <v>914</v>
       </c>
@@ -11291,7 +11282,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3">
       <c r="A339" s="3" t="s">
         <v>917</v>
       </c>
@@ -11302,7 +11293,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3">
       <c r="A340" s="2" t="s">
         <v>920</v>
       </c>
@@ -11313,7 +11304,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3">
       <c r="A341" s="3" t="s">
         <v>923</v>
       </c>
@@ -11324,7 +11315,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3">
       <c r="A342" s="2" t="s">
         <v>926</v>
       </c>
@@ -11335,7 +11326,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3">
       <c r="A343" s="3" t="s">
         <v>927</v>
       </c>
@@ -11346,7 +11337,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3">
       <c r="A344" s="2" t="s">
         <v>929</v>
       </c>
@@ -11357,7 +11348,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3">
       <c r="A345" s="3" t="s">
         <v>932</v>
       </c>
@@ -11368,7 +11359,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3">
       <c r="A346" s="2" t="s">
         <v>935</v>
       </c>
@@ -11379,7 +11370,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3">
       <c r="A347" s="3" t="s">
         <v>938</v>
       </c>
@@ -11390,7 +11381,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3">
       <c r="A348" s="2" t="s">
         <v>941</v>
       </c>
@@ -11401,7 +11392,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3">
       <c r="A349" s="3" t="s">
         <v>944</v>
       </c>
@@ -11412,7 +11403,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3">
       <c r="A350" s="2" t="s">
         <v>947</v>
       </c>
@@ -11423,7 +11414,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3">
       <c r="A351" s="3" t="s">
         <v>950</v>
       </c>
@@ -11434,7 +11425,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3">
       <c r="A352" s="2" t="s">
         <v>953</v>
       </c>
@@ -11445,7 +11436,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3">
       <c r="A353" s="3" t="s">
         <v>956</v>
       </c>
@@ -11456,7 +11447,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3">
       <c r="A354" s="2" t="s">
         <v>959</v>
       </c>
@@ -11467,7 +11458,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3">
       <c r="A355" s="3" t="s">
         <v>962</v>
       </c>
@@ -11478,7 +11469,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3">
       <c r="A356" s="2" t="s">
         <v>965</v>
       </c>
@@ -11489,7 +11480,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3">
       <c r="A357" s="3" t="s">
         <v>968</v>
       </c>
@@ -11500,7 +11491,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3">
       <c r="A358" s="2" t="s">
         <v>971</v>
       </c>
@@ -11511,7 +11502,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3">
       <c r="A359" s="3" t="s">
         <v>974</v>
       </c>
@@ -11522,7 +11513,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3">
       <c r="A360" s="2" t="s">
         <v>977</v>
       </c>
@@ -11533,7 +11524,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3">
       <c r="A361" s="3" t="s">
         <v>980</v>
       </c>
@@ -11544,7 +11535,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3">
       <c r="A362" s="2" t="s">
         <v>983</v>
       </c>
@@ -11555,7 +11546,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3">
       <c r="A363" s="3" t="s">
         <v>986</v>
       </c>
@@ -11566,7 +11557,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3">
       <c r="A364" s="2" t="s">
         <v>988</v>
       </c>
@@ -11577,7 +11568,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3">
       <c r="A365" s="3" t="s">
         <v>991</v>
       </c>
@@ -11588,7 +11579,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3">
       <c r="A366" s="2" t="s">
         <v>994</v>
       </c>
@@ -11599,7 +11590,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3">
       <c r="A367" s="3" t="s">
         <v>997</v>
       </c>
@@ -11610,7 +11601,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3">
       <c r="A368" s="2" t="s">
         <v>1000</v>
       </c>
@@ -11621,7 +11612,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3">
       <c r="A369" s="3" t="s">
         <v>1003</v>
       </c>
@@ -11632,7 +11623,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3">
       <c r="A370" s="2" t="s">
         <v>1006</v>
       </c>
@@ -11643,7 +11634,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3">
       <c r="A371" s="3" t="s">
         <v>1009</v>
       </c>
@@ -11654,7 +11645,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3">
       <c r="A372" s="2" t="s">
         <v>1012</v>
       </c>
@@ -11665,7 +11656,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3">
       <c r="A373" s="3" t="s">
         <v>1015</v>
       </c>
@@ -11676,7 +11667,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3">
       <c r="A374" s="2" t="s">
         <v>1018</v>
       </c>
@@ -11687,7 +11678,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3">
       <c r="A375" s="3" t="s">
         <v>1021</v>
       </c>
@@ -11698,7 +11689,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3">
       <c r="A376" s="2" t="s">
         <v>1024</v>
       </c>
@@ -11709,7 +11700,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3">
       <c r="A377" s="3" t="s">
         <v>1027</v>
       </c>
@@ -11720,7 +11711,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3">
       <c r="A378" s="2" t="s">
         <v>1030</v>
       </c>
@@ -11731,7 +11722,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3">
       <c r="A379" s="3" t="s">
         <v>1033</v>
       </c>
@@ -11742,7 +11733,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3">
       <c r="A380" s="2" t="s">
         <v>1036</v>
       </c>
@@ -11753,7 +11744,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3">
       <c r="A381" s="3" t="s">
         <v>1039</v>
       </c>
@@ -11764,7 +11755,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3">
       <c r="A382" s="2" t="s">
         <v>1042</v>
       </c>
@@ -11775,7 +11766,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3">
       <c r="A383" s="3" t="s">
         <v>1045</v>
       </c>
@@ -11786,7 +11777,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3">
       <c r="A384" s="2" t="s">
         <v>1048</v>
       </c>
@@ -11797,7 +11788,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3">
       <c r="A385" s="3" t="s">
         <v>1051</v>
       </c>
@@ -11808,7 +11799,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3">
       <c r="A386" s="2" t="s">
         <v>1054</v>
       </c>
@@ -11819,7 +11810,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3">
       <c r="A387" s="3" t="s">
         <v>1057</v>
       </c>
@@ -11830,7 +11821,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3">
       <c r="A388" s="2" t="s">
         <v>1060</v>
       </c>
@@ -11841,7 +11832,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3">
       <c r="A389" s="3" t="s">
         <v>1063</v>
       </c>
@@ -11852,7 +11843,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3">
       <c r="A390" s="2" t="s">
         <v>1066</v>
       </c>
@@ -11863,7 +11854,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3">
       <c r="A391" s="3" t="s">
         <v>1069</v>
       </c>
@@ -11874,7 +11865,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3">
       <c r="A392" s="2" t="s">
         <v>1072</v>
       </c>
@@ -11885,7 +11876,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3">
       <c r="A393" s="3" t="s">
         <v>1075</v>
       </c>
@@ -11896,7 +11887,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3">
       <c r="A394" s="2" t="s">
         <v>1078</v>
       </c>
@@ -11907,7 +11898,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3">
       <c r="A395" s="3" t="s">
         <v>1081</v>
       </c>
@@ -11918,7 +11909,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3">
       <c r="A396" s="2" t="s">
         <v>1084</v>
       </c>
@@ -11929,7 +11920,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3">
       <c r="A397" s="3" t="s">
         <v>1087</v>
       </c>
@@ -11940,7 +11931,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3">
       <c r="A398" s="2" t="s">
         <v>1090</v>
       </c>
@@ -11951,7 +11942,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3">
       <c r="A399" s="3" t="s">
         <v>1093</v>
       </c>
@@ -11962,7 +11953,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3">
       <c r="A400" s="2" t="s">
         <v>1096</v>
       </c>
@@ -11973,7 +11964,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3">
       <c r="A401" s="3" t="s">
         <v>1099</v>
       </c>
@@ -11984,7 +11975,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3">
       <c r="A402" s="2" t="s">
         <v>1102</v>
       </c>
@@ -11995,7 +11986,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3">
       <c r="A403" s="3" t="s">
         <v>1105</v>
       </c>
@@ -12006,7 +11997,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3">
       <c r="A404" s="2" t="s">
         <v>1108</v>
       </c>
@@ -12017,7 +12008,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3">
       <c r="A405" s="3" t="s">
         <v>1111</v>
       </c>
@@ -12028,7 +12019,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3">
       <c r="A406" s="2" t="s">
         <v>1114</v>
       </c>
@@ -12039,7 +12030,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3">
       <c r="A407" s="3" t="s">
         <v>1117</v>
       </c>
@@ -12050,7 +12041,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3">
       <c r="A408" s="2" t="s">
         <v>1120</v>
       </c>
@@ -12061,7 +12052,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3">
       <c r="A409" s="3" t="s">
         <v>1123</v>
       </c>
@@ -12072,7 +12063,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3">
       <c r="A410" s="2" t="s">
         <v>1126</v>
       </c>
@@ -12083,7 +12074,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3">
       <c r="A411" s="3" t="s">
         <v>1129</v>
       </c>
@@ -12094,7 +12085,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3">
       <c r="A412" s="2" t="s">
         <v>1132</v>
       </c>
@@ -12105,7 +12096,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3">
       <c r="A413" s="3" t="s">
         <v>1135</v>
       </c>
@@ -12116,7 +12107,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3">
       <c r="A414" s="2" t="s">
         <v>1138</v>
       </c>
@@ -12127,7 +12118,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3">
       <c r="A415" s="3" t="s">
         <v>1141</v>
       </c>
@@ -12138,7 +12129,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3">
       <c r="A416" s="2" t="s">
         <v>1144</v>
       </c>
@@ -12149,7 +12140,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3">
       <c r="A417" s="3" t="s">
         <v>1147</v>
       </c>
@@ -12160,7 +12151,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3">
       <c r="A418" s="2" t="s">
         <v>1150</v>
       </c>
@@ -12171,7 +12162,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3">
       <c r="A419" s="3" t="s">
         <v>1153</v>
       </c>
@@ -12182,7 +12173,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3">
       <c r="A420" s="2" t="s">
         <v>1156</v>
       </c>
@@ -12193,7 +12184,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3">
       <c r="A421" s="3" t="s">
         <v>1159</v>
       </c>
@@ -12204,7 +12195,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3">
       <c r="A422" s="2" t="s">
         <v>1162</v>
       </c>
@@ -12215,7 +12206,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3">
       <c r="A423" s="3" t="s">
         <v>1165</v>
       </c>
@@ -12226,7 +12217,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3">
       <c r="A424" s="2" t="s">
         <v>1168</v>
       </c>
@@ -12237,7 +12228,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3">
       <c r="A425" s="3" t="s">
         <v>1171</v>
       </c>
@@ -12248,7 +12239,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3">
       <c r="A426" s="2" t="s">
         <v>1174</v>
       </c>
@@ -12259,7 +12250,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3">
       <c r="A427" s="3" t="s">
         <v>1175</v>
       </c>
@@ -12270,7 +12261,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3">
       <c r="A428" s="2" t="s">
         <v>1178</v>
       </c>
@@ -12281,7 +12272,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3">
       <c r="A429" s="3" t="s">
         <v>1181</v>
       </c>
@@ -12292,7 +12283,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3">
       <c r="A430" s="2" t="s">
         <v>1184</v>
       </c>
@@ -12303,7 +12294,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3">
       <c r="A431" s="3" t="s">
         <v>1187</v>
       </c>
@@ -12314,7 +12305,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3">
       <c r="A432" s="2" t="s">
         <v>1190</v>
       </c>
@@ -12325,7 +12316,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3">
       <c r="A433" s="3" t="s">
         <v>1193</v>
       </c>
@@ -12336,7 +12327,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3">
       <c r="A434" s="2" t="s">
         <v>1196</v>
       </c>
@@ -12347,7 +12338,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3">
       <c r="A435" s="3" t="s">
         <v>1199</v>
       </c>
@@ -12358,7 +12349,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3">
       <c r="A436" s="2" t="s">
         <v>1202</v>
       </c>
@@ -12369,7 +12360,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3">
       <c r="A437" s="3" t="s">
         <v>1205</v>
       </c>
@@ -12380,7 +12371,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3">
       <c r="A438" s="2" t="s">
         <v>1208</v>
       </c>
@@ -12391,7 +12382,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3">
       <c r="A439" s="3" t="s">
         <v>1211</v>
       </c>
@@ -12402,7 +12393,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3">
       <c r="A440" s="2" t="s">
         <v>1214</v>
       </c>
@@ -12413,7 +12404,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3">
       <c r="A441" s="3" t="s">
         <v>1217</v>
       </c>
@@ -12424,7 +12415,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3">
       <c r="A442" s="2" t="s">
         <v>1220</v>
       </c>
@@ -12435,7 +12426,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3">
       <c r="A443" s="3" t="s">
         <v>1223</v>
       </c>
@@ -12446,7 +12437,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3">
       <c r="A444" s="2" t="s">
         <v>1226</v>
       </c>
@@ -12457,7 +12448,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3">
       <c r="A445" s="3" t="s">
         <v>1229</v>
       </c>
@@ -12468,7 +12459,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3">
       <c r="A446" s="2" t="s">
         <v>1232</v>
       </c>
@@ -12479,7 +12470,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3">
       <c r="A447" s="3" t="s">
         <v>1235</v>
       </c>
@@ -12490,7 +12481,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3">
       <c r="A448" s="2" t="s">
         <v>1238</v>
       </c>
@@ -12501,7 +12492,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3">
       <c r="A449" s="3" t="s">
         <v>1241</v>
       </c>
@@ -12512,7 +12503,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3">
       <c r="A450" s="2" t="s">
         <v>1244</v>
       </c>
@@ -12523,7 +12514,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3">
       <c r="A451" s="3" t="s">
         <v>1247</v>
       </c>
@@ -12534,7 +12525,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3">
       <c r="A452" s="2" t="s">
         <v>1250</v>
       </c>
@@ -12545,7 +12536,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3">
       <c r="A453" s="3" t="s">
         <v>1253</v>
       </c>
@@ -12556,7 +12547,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3">
       <c r="A454" s="2" t="s">
         <v>1256</v>
       </c>
@@ -12567,7 +12558,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3">
       <c r="A455" s="3" t="s">
         <v>1259</v>
       </c>
@@ -12578,7 +12569,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3">
       <c r="A456" s="2" t="s">
         <v>1262</v>
       </c>
@@ -12589,7 +12580,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3">
       <c r="A457" s="3" t="s">
         <v>1265</v>
       </c>
@@ -12600,7 +12591,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3">
       <c r="A458" s="2" t="s">
         <v>1268</v>
       </c>
@@ -12611,7 +12602,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3">
       <c r="A459" s="3" t="s">
         <v>1271</v>
       </c>
@@ -12622,7 +12613,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3">
       <c r="A460" s="2" t="s">
         <v>1274</v>
       </c>
@@ -12633,7 +12624,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3">
       <c r="A461" s="3" t="s">
         <v>1277</v>
       </c>
@@ -12644,7 +12635,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3">
       <c r="A462" s="2" t="s">
         <v>1280</v>
       </c>
@@ -12655,7 +12646,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3">
       <c r="A463" s="3" t="s">
         <v>1283</v>
       </c>
@@ -12666,7 +12657,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3">
       <c r="A464" s="2" t="s">
         <v>1286</v>
       </c>
@@ -12677,7 +12668,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3">
       <c r="A465" s="3" t="s">
         <v>1289</v>
       </c>
@@ -12688,7 +12679,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3">
       <c r="A466" s="2" t="s">
         <v>1292</v>
       </c>
@@ -12699,7 +12690,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3">
       <c r="A467" s="3" t="s">
         <v>1295</v>
       </c>
@@ -12710,7 +12701,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3">
       <c r="A468" s="2" t="s">
         <v>1298</v>
       </c>
@@ -12721,7 +12712,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3">
       <c r="A469" s="3" t="s">
         <v>1301</v>
       </c>
@@ -12732,7 +12723,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3">
       <c r="A470" s="2" t="s">
         <v>1304</v>
       </c>
@@ -12743,7 +12734,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3">
       <c r="A471" s="3" t="s">
         <v>1307</v>
       </c>
@@ -12754,7 +12745,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3">
       <c r="A472" s="2" t="s">
         <v>1310</v>
       </c>
@@ -12765,7 +12756,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3">
       <c r="A473" s="3" t="s">
         <v>1313</v>
       </c>
@@ -12776,7 +12767,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3">
       <c r="A474" s="2" t="s">
         <v>1316</v>
       </c>
@@ -12787,7 +12778,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3">
       <c r="A475" s="3" t="s">
         <v>1319</v>
       </c>
@@ -12798,7 +12789,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3">
       <c r="A476" s="2" t="s">
         <v>1321</v>
       </c>
@@ -12809,7 +12800,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3">
       <c r="A477" s="3" t="s">
         <v>1324</v>
       </c>
@@ -12820,7 +12811,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3">
       <c r="A478" s="2" t="s">
         <v>1326</v>
       </c>
@@ -12831,7 +12822,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3">
       <c r="A479" s="3" t="s">
         <v>1329</v>
       </c>
@@ -12842,7 +12833,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3">
       <c r="A480" s="2" t="s">
         <v>1333</v>
       </c>
@@ -12853,7 +12844,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3">
       <c r="A481" s="3" t="s">
         <v>1336</v>
       </c>
@@ -12864,7 +12855,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3">
       <c r="A482" s="2" t="s">
         <v>1339</v>
       </c>
@@ -12875,7 +12866,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3">
       <c r="A483" s="3" t="s">
         <v>1342</v>
       </c>
@@ -12886,7 +12877,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3">
       <c r="A484" s="2" t="s">
         <v>1345</v>
       </c>
@@ -12897,7 +12888,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3">
       <c r="A485" s="3" t="s">
         <v>1348</v>
       </c>
@@ -12908,7 +12899,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3">
       <c r="A486" s="2" t="s">
         <v>1351</v>
       </c>
@@ -12919,7 +12910,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3">
       <c r="A487" s="3" t="s">
         <v>1354</v>
       </c>
@@ -12930,7 +12921,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3">
       <c r="A488" s="2" t="s">
         <v>1357</v>
       </c>
@@ -12941,7 +12932,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3">
       <c r="A489" s="3" t="s">
         <v>1360</v>
       </c>
@@ -12952,7 +12943,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3">
       <c r="A490" s="2" t="s">
         <v>1363</v>
       </c>
@@ -12963,7 +12954,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3">
       <c r="A491" s="3" t="s">
         <v>1366</v>
       </c>
@@ -12974,7 +12965,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3">
       <c r="A492" s="2" t="s">
         <v>1369</v>
       </c>
@@ -12985,7 +12976,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3">
       <c r="A493" s="3" t="s">
         <v>1372</v>
       </c>
@@ -12996,7 +12987,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3">
       <c r="A494" s="2" t="s">
         <v>1375</v>
       </c>
@@ -13007,7 +12998,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3">
       <c r="A495" s="3" t="s">
         <v>1378</v>
       </c>
@@ -13018,7 +13009,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3">
       <c r="A496" s="2" t="s">
         <v>1381</v>
       </c>
@@ -13029,7 +13020,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3">
       <c r="A497" s="3" t="s">
         <v>1384</v>
       </c>
@@ -13040,7 +13031,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3">
       <c r="A498" s="2" t="s">
         <v>1387</v>
       </c>
@@ -13051,7 +13042,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3">
       <c r="A499" s="3" t="s">
         <v>1390</v>
       </c>
@@ -13062,7 +13053,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3">
       <c r="A500" s="2" t="s">
         <v>1393</v>
       </c>
@@ -13073,7 +13064,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3">
       <c r="A501" s="3" t="s">
         <v>1396</v>
       </c>
@@ -13084,7 +13075,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3">
       <c r="A502" s="2" t="s">
         <v>1399</v>
       </c>
@@ -13095,7 +13086,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3">
       <c r="A503" s="3" t="s">
         <v>1402</v>
       </c>
@@ -13106,7 +13097,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3">
       <c r="A504" s="2" t="s">
         <v>1405</v>
       </c>
@@ -13117,7 +13108,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3">
       <c r="A505" s="3" t="s">
         <v>1408</v>
       </c>
@@ -13128,7 +13119,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3">
       <c r="A506" s="2" t="s">
         <v>1411</v>
       </c>
@@ -13139,7 +13130,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3">
       <c r="A507" s="3" t="s">
         <v>1414</v>
       </c>
@@ -13150,7 +13141,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3">
       <c r="A508" s="2" t="s">
         <v>1417</v>
       </c>
@@ -13161,7 +13152,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3">
       <c r="A509" s="3" t="s">
         <v>1420</v>
       </c>
@@ -13172,7 +13163,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3">
       <c r="A510" s="2" t="s">
         <v>1423</v>
       </c>
@@ -13183,7 +13174,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3">
       <c r="A511" s="3" t="s">
         <v>1426</v>
       </c>
@@ -13194,7 +13185,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3">
       <c r="A512" s="2" t="s">
         <v>1429</v>
       </c>
@@ -13205,7 +13196,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3">
       <c r="A513" s="3" t="s">
         <v>1432</v>
       </c>
@@ -13216,7 +13207,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3">
       <c r="A514" s="2" t="s">
         <v>1435</v>
       </c>
@@ -13227,7 +13218,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3">
       <c r="A515" s="3" t="s">
         <v>1438</v>
       </c>
@@ -13238,7 +13229,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3">
       <c r="A516" s="2" t="s">
         <v>1441</v>
       </c>
@@ -13249,7 +13240,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3">
       <c r="A517" s="3" t="s">
         <v>1443</v>
       </c>
@@ -13260,7 +13251,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3">
       <c r="A518" s="2" t="s">
         <v>1446</v>
       </c>
@@ -13271,7 +13262,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3">
       <c r="A519" s="3" t="s">
         <v>1449</v>
       </c>
@@ -13282,7 +13273,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3">
       <c r="A520" s="2" t="s">
         <v>1452</v>
       </c>
@@ -13293,7 +13284,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3">
       <c r="A521" s="3" t="s">
         <v>1455</v>
       </c>
@@ -13304,7 +13295,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3">
       <c r="A522" s="2" t="s">
         <v>1458</v>
       </c>
@@ -13315,7 +13306,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3">
       <c r="A523" s="3" t="s">
         <v>1461</v>
       </c>
@@ -13326,7 +13317,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3">
       <c r="A524" s="2" t="s">
         <v>1464</v>
       </c>
@@ -13337,7 +13328,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3">
       <c r="A525" s="3" t="s">
         <v>1467</v>
       </c>
@@ -13348,7 +13339,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:3">
       <c r="A526" s="2" t="s">
         <v>1470</v>
       </c>
@@ -13359,7 +13350,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:3">
       <c r="A527" s="3" t="s">
         <v>1473</v>
       </c>
@@ -13370,7 +13361,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:3">
       <c r="A528" s="2" t="s">
         <v>1476</v>
       </c>
@@ -13381,7 +13372,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:3">
       <c r="A529" s="3" t="s">
         <v>1479</v>
       </c>
@@ -13392,7 +13383,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:3">
       <c r="A530" s="2" t="s">
         <v>1482</v>
       </c>
@@ -13403,7 +13394,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:3">
       <c r="A531" s="3" t="s">
         <v>1485</v>
       </c>
@@ -13414,7 +13405,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:3">
       <c r="A532" s="2" t="s">
         <v>1488</v>
       </c>
@@ -13425,7 +13416,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:3">
       <c r="A533" s="3" t="s">
         <v>1491</v>
       </c>
@@ -13436,7 +13427,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:3">
       <c r="A534" s="2" t="s">
         <v>1494</v>
       </c>
@@ -13447,7 +13438,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:3">
       <c r="A535" s="3" t="s">
         <v>1497</v>
       </c>
@@ -13458,7 +13449,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:3">
       <c r="A536" s="2" t="s">
         <v>1500</v>
       </c>
@@ -13469,7 +13460,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:3">
       <c r="A537" s="3" t="s">
         <v>1503</v>
       </c>
@@ -13480,7 +13471,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:3">
       <c r="A538" s="2" t="s">
         <v>1506</v>
       </c>
@@ -13491,7 +13482,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:3">
       <c r="A539" s="3" t="s">
         <v>1509</v>
       </c>
@@ -13502,7 +13493,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:3">
       <c r="A540" s="2" t="s">
         <v>1512</v>
       </c>
@@ -13513,7 +13504,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:3">
       <c r="A541" s="3" t="s">
         <v>1515</v>
       </c>
@@ -13524,7 +13515,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:3">
       <c r="A542" s="2" t="s">
         <v>1518</v>
       </c>
@@ -13535,7 +13526,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:3">
       <c r="A543" s="3" t="s">
         <v>1521</v>
       </c>
@@ -13546,7 +13537,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:3">
       <c r="A544" s="2" t="s">
         <v>1524</v>
       </c>
@@ -13557,7 +13548,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3">
       <c r="A545" s="3" t="s">
         <v>1527</v>
       </c>
@@ -13568,7 +13559,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:3">
       <c r="A546" s="2" t="s">
         <v>1530</v>
       </c>
@@ -13579,7 +13570,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:3">
       <c r="A547" s="3" t="s">
         <v>1533</v>
       </c>
@@ -13590,7 +13581,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:3">
       <c r="A548" s="2" t="s">
         <v>1536</v>
       </c>
@@ -13601,7 +13592,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3">
       <c r="A549" s="3" t="s">
         <v>1539</v>
       </c>
@@ -13612,7 +13603,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:3">
       <c r="A550" s="2" t="s">
         <v>1542</v>
       </c>
@@ -13623,7 +13614,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:3">
       <c r="A551" s="3" t="s">
         <v>1545</v>
       </c>
@@ -13634,7 +13625,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:3">
       <c r="A552" s="2" t="s">
         <v>1548</v>
       </c>
@@ -13645,7 +13636,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:3">
       <c r="A553" s="3" t="s">
         <v>1551</v>
       </c>
@@ -13656,7 +13647,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:3">
       <c r="A554" s="2" t="s">
         <v>1554</v>
       </c>
@@ -13667,7 +13658,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:3">
       <c r="A555" s="3" t="s">
         <v>1557</v>
       </c>
@@ -13678,7 +13669,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:3">
       <c r="A556" s="2" t="s">
         <v>1560</v>
       </c>
@@ -13689,7 +13680,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:3">
       <c r="A557" s="3" t="s">
         <v>1562</v>
       </c>
@@ -13700,7 +13691,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:3">
       <c r="A558" s="2" t="s">
         <v>1565</v>
       </c>
@@ -13711,7 +13702,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:3">
       <c r="A559" s="3" t="s">
         <v>1568</v>
       </c>
@@ -13722,7 +13713,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:3">
       <c r="A560" s="2" t="s">
         <v>1571</v>
       </c>
@@ -13733,7 +13724,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:3">
       <c r="A561" s="3" t="s">
         <v>1574</v>
       </c>
@@ -13744,7 +13735,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:3">
       <c r="A562" s="2" t="s">
         <v>1577</v>
       </c>
@@ -13755,7 +13746,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:3">
       <c r="A563" s="3" t="s">
         <v>1580</v>
       </c>
@@ -13766,7 +13757,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:3">
       <c r="A564" s="2" t="s">
         <v>1583</v>
       </c>
@@ -13777,7 +13768,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:3">
       <c r="A565" s="3" t="s">
         <v>1586</v>
       </c>
@@ -13788,7 +13779,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:3">
       <c r="A566" s="2" t="s">
         <v>1589</v>
       </c>
@@ -13799,7 +13790,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:3">
       <c r="A567" s="3" t="s">
         <v>1592</v>
       </c>
@@ -13810,7 +13801,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:3">
       <c r="A568" s="2" t="s">
         <v>1595</v>
       </c>
@@ -13821,7 +13812,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:3">
       <c r="A569" s="3" t="s">
         <v>1598</v>
       </c>
@@ -13832,7 +13823,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:3">
       <c r="A570" s="2" t="s">
         <v>1601</v>
       </c>
@@ -13843,7 +13834,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:3">
       <c r="A571" s="3" t="s">
         <v>1604</v>
       </c>
@@ -13854,7 +13845,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:3">
       <c r="A572" s="2" t="s">
         <v>1607</v>
       </c>
@@ -13865,7 +13856,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:3">
       <c r="A573" s="3" t="s">
         <v>1610</v>
       </c>
@@ -13876,7 +13867,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:3">
       <c r="A574" s="2" t="s">
         <v>1613</v>
       </c>
@@ -13887,7 +13878,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:3">
       <c r="A575" s="3" t="s">
         <v>1616</v>
       </c>
@@ -13898,7 +13889,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:3">
       <c r="A576" s="2" t="s">
         <v>1619</v>
       </c>
@@ -13909,7 +13900,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:3">
       <c r="A577" s="3" t="s">
         <v>1622</v>
       </c>
@@ -13920,7 +13911,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:3">
       <c r="A578" s="2" t="s">
         <v>1625</v>
       </c>
@@ -13931,7 +13922,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:3">
       <c r="A579" s="3" t="s">
         <v>1628</v>
       </c>
@@ -13942,7 +13933,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:3">
       <c r="A580" s="2" t="s">
         <v>1631</v>
       </c>
@@ -13953,7 +13944,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:3">
       <c r="A581" s="3" t="s">
         <v>1634</v>
       </c>
@@ -13964,7 +13955,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:3">
       <c r="A582" s="2" t="s">
         <v>1637</v>
       </c>
@@ -13975,7 +13966,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:3">
       <c r="A583" s="3" t="s">
         <v>1640</v>
       </c>
@@ -13986,7 +13977,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:3">
       <c r="A584" s="2" t="s">
         <v>1643</v>
       </c>
@@ -13997,7 +13988,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:3">
       <c r="A585" s="3" t="s">
         <v>1646</v>
       </c>
@@ -14008,7 +13999,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:3">
       <c r="A586" s="2" t="s">
         <v>1649</v>
       </c>
@@ -14019,7 +14010,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:3">
       <c r="A587" s="3" t="s">
         <v>1652</v>
       </c>
@@ -14030,7 +14021,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:3">
       <c r="A588" s="2" t="s">
         <v>1655</v>
       </c>
@@ -14041,7 +14032,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:3">
       <c r="A589" s="3" t="s">
         <v>1658</v>
       </c>
@@ -14052,7 +14043,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:3">
       <c r="A590" s="2" t="s">
         <v>1661</v>
       </c>
@@ -14063,7 +14054,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:3">
       <c r="A591" s="3" t="s">
         <v>1664</v>
       </c>
@@ -14074,7 +14065,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:3">
       <c r="A592" s="2" t="s">
         <v>1667</v>
       </c>
@@ -14085,7 +14076,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:3">
       <c r="A593" s="3" t="s">
         <v>1670</v>
       </c>
@@ -14096,7 +14087,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:3">
       <c r="A594" s="2" t="s">
         <v>1672</v>
       </c>
@@ -14107,7 +14098,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:3">
       <c r="A595" s="3" t="s">
         <v>1675</v>
       </c>
@@ -14118,7 +14109,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:3">
       <c r="A596" s="2" t="s">
         <v>1678</v>
       </c>
@@ -14129,7 +14120,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:3">
       <c r="A597" s="3" t="s">
         <v>1681</v>
       </c>
@@ -14140,7 +14131,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:3">
       <c r="A598" s="2" t="s">
         <v>1684</v>
       </c>
@@ -14151,7 +14142,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:3">
       <c r="A599" s="3" t="s">
         <v>1687</v>
       </c>
@@ -14162,7 +14153,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:3">
       <c r="A600" s="2" t="s">
         <v>1690</v>
       </c>
@@ -14173,7 +14164,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:3">
       <c r="A601" s="3" t="s">
         <v>1693</v>
       </c>
@@ -14184,7 +14175,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:3">
       <c r="A602" s="2" t="s">
         <v>1696</v>
       </c>
@@ -14195,7 +14186,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:3">
       <c r="A603" s="3" t="s">
         <v>1699</v>
       </c>
@@ -14206,7 +14197,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:3">
       <c r="A604" s="2" t="s">
         <v>1702</v>
       </c>
@@ -14217,7 +14208,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:3">
       <c r="A605" s="3" t="s">
         <v>1705</v>
       </c>
@@ -14228,7 +14219,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:3">
       <c r="A606" s="2" t="s">
         <v>1708</v>
       </c>
@@ -14239,7 +14230,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:3">
       <c r="A607" s="3" t="s">
         <v>1711</v>
       </c>
@@ -14250,7 +14241,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:3">
       <c r="A608" s="2" t="s">
         <v>1714</v>
       </c>
@@ -14261,7 +14252,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:3">
       <c r="A609" s="3" t="s">
         <v>1717</v>
       </c>
@@ -14272,7 +14263,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:3">
       <c r="A610" s="2" t="s">
         <v>1720</v>
       </c>
@@ -14283,7 +14274,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:3">
       <c r="A611" s="3" t="s">
         <v>1723</v>
       </c>
@@ -14294,7 +14285,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:3">
       <c r="A612" s="2" t="s">
         <v>1726</v>
       </c>
@@ -14305,7 +14296,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:3">
       <c r="A613" s="3" t="s">
         <v>1729</v>
       </c>
@@ -14316,7 +14307,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:3">
       <c r="A614" s="2" t="s">
         <v>1732</v>
       </c>
@@ -14327,7 +14318,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:3">
       <c r="A615" s="3" t="s">
         <v>1735</v>
       </c>
@@ -14338,7 +14329,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:3">
       <c r="A616" s="2" t="s">
         <v>1738</v>
       </c>
@@ -14349,7 +14340,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:3">
       <c r="A617" s="3" t="s">
         <v>1741</v>
       </c>
@@ -14360,7 +14351,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:3">
       <c r="A618" s="2" t="s">
         <v>1744</v>
       </c>
@@ -14371,7 +14362,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:3">
       <c r="A619" s="3" t="s">
         <v>1747</v>
       </c>
@@ -14382,7 +14373,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:3">
       <c r="A620" s="2" t="s">
         <v>1750</v>
       </c>
@@ -14393,7 +14384,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:3">
       <c r="A621" s="3" t="s">
         <v>1753</v>
       </c>
@@ -14404,7 +14395,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:3">
       <c r="A622" s="2" t="s">
         <v>1756</v>
       </c>
@@ -14415,7 +14406,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:3">
       <c r="A623" s="3" t="s">
         <v>1759</v>
       </c>
@@ -14426,7 +14417,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:3">
       <c r="A624" s="2" t="s">
         <v>1762</v>
       </c>
@@ -14437,7 +14428,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:3">
       <c r="A625" s="3" t="s">
         <v>1765</v>
       </c>
@@ -14448,7 +14439,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:3">
       <c r="A626" s="2" t="s">
         <v>1768</v>
       </c>
@@ -14459,7 +14450,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:3">
       <c r="A627" s="3" t="s">
         <v>1771</v>
       </c>
@@ -14470,7 +14461,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:3">
       <c r="A628" s="2" t="s">
         <v>1774</v>
       </c>
@@ -14481,7 +14472,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:3">
       <c r="A629" s="3" t="s">
         <v>1777</v>
       </c>
@@ -14492,7 +14483,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:3">
       <c r="A630" s="2" t="s">
         <v>1780</v>
       </c>
@@ -14503,7 +14494,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:3">
       <c r="A631" s="3" t="s">
         <v>1783</v>
       </c>
@@ -14514,7 +14505,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:3">
       <c r="A632" s="2" t="s">
         <v>1786</v>
       </c>
@@ -14525,7 +14516,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:3">
       <c r="A633" s="3" t="s">
         <v>1789</v>
       </c>
@@ -14536,7 +14527,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:3">
       <c r="A634" s="2" t="s">
         <v>1792</v>
       </c>
@@ -14547,7 +14538,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:3">
       <c r="A635" s="3" t="s">
         <v>1795</v>
       </c>
@@ -14558,7 +14549,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:3">
       <c r="A636" s="2" t="s">
         <v>1798</v>
       </c>
@@ -14569,7 +14560,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:3">
       <c r="A637" s="3" t="s">
         <v>1801</v>
       </c>
@@ -14580,7 +14571,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:3">
       <c r="A638" s="2" t="s">
         <v>1804</v>
       </c>
@@ -14591,7 +14582,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:3">
       <c r="A639" s="3" t="s">
         <v>1807</v>
       </c>
@@ -14602,7 +14593,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:3">
       <c r="A640" s="2" t="s">
         <v>1810</v>
       </c>
@@ -14613,7 +14604,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:3">
       <c r="A641" s="3" t="s">
         <v>1813</v>
       </c>
@@ -14624,7 +14615,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:3">
       <c r="A642" s="2" t="s">
         <v>1816</v>
       </c>
@@ -14635,7 +14626,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:3">
       <c r="A643" s="3" t="s">
         <v>1819</v>
       </c>
@@ -14646,7 +14637,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:3">
       <c r="A644" s="2" t="s">
         <v>1822</v>
       </c>
@@ -14657,7 +14648,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:3">
       <c r="A645" s="3" t="s">
         <v>1825</v>
       </c>
@@ -14668,7 +14659,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:3">
       <c r="A646" s="2" t="s">
         <v>1828</v>
       </c>
@@ -14679,7 +14670,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:3">
       <c r="A647" s="3" t="s">
         <v>1831</v>
       </c>
@@ -14690,7 +14681,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:3">
       <c r="A648" s="2" t="s">
         <v>1834</v>
       </c>
@@ -14701,7 +14692,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:3">
       <c r="A649" s="3" t="s">
         <v>1837</v>
       </c>
@@ -14712,7 +14703,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:3">
       <c r="A650" s="2" t="s">
         <v>1840</v>
       </c>
@@ -14723,7 +14714,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:3">
       <c r="A651" s="3" t="s">
         <v>1843</v>
       </c>
@@ -14734,7 +14725,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:3">
       <c r="A652" s="2" t="s">
         <v>1846</v>
       </c>
@@ -14745,7 +14736,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:3">
       <c r="A653" s="3" t="s">
         <v>1849</v>
       </c>
@@ -14756,7 +14747,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:3">
       <c r="A654" s="2" t="s">
         <v>1852</v>
       </c>
@@ -14767,7 +14758,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:3">
       <c r="A655" s="3" t="s">
         <v>1855</v>
       </c>
@@ -14778,7 +14769,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:3">
       <c r="A656" s="2" t="s">
         <v>1858</v>
       </c>
@@ -14789,7 +14780,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:3">
       <c r="A657" s="3" t="s">
         <v>1861</v>
       </c>
@@ -14800,7 +14791,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:3">
       <c r="A658" s="2" t="s">
         <v>1864</v>
       </c>
@@ -14811,7 +14802,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:3">
       <c r="A659" s="3" t="s">
         <v>1867</v>
       </c>
@@ -14822,7 +14813,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:3">
       <c r="A660" s="2" t="s">
         <v>1870</v>
       </c>
@@ -14833,7 +14824,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:3">
       <c r="A661" s="3" t="s">
         <v>1873</v>
       </c>
@@ -14844,7 +14835,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:3">
       <c r="A662" s="2" t="s">
         <v>1876</v>
       </c>
@@ -14855,7 +14846,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:3">
       <c r="A663" s="3" t="s">
         <v>1879</v>
       </c>
@@ -14866,7 +14857,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:3">
       <c r="A664" s="2" t="s">
         <v>1882</v>
       </c>
@@ -14877,7 +14868,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:3">
       <c r="A665" s="3" t="s">
         <v>1885</v>
       </c>
@@ -14888,7 +14879,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:3">
       <c r="A666" s="2" t="s">
         <v>1888</v>
       </c>
@@ -14899,7 +14890,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:3">
       <c r="A667" s="3" t="s">
         <v>1891</v>
       </c>
@@ -14910,7 +14901,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:3">
       <c r="A668" s="2" t="s">
         <v>1894</v>
       </c>
@@ -14921,7 +14912,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:3">
       <c r="A669" s="3" t="s">
         <v>1897</v>
       </c>
@@ -14932,7 +14923,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:3">
       <c r="A670" s="2" t="s">
         <v>1900</v>
       </c>
@@ -14943,7 +14934,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:3">
       <c r="A671" s="3" t="s">
         <v>1903</v>
       </c>
@@ -14954,7 +14945,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:3">
       <c r="A672" s="2" t="s">
         <v>1906</v>
       </c>
@@ -14965,7 +14956,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:3">
       <c r="A673" s="3" t="s">
         <v>1909</v>
       </c>
@@ -14976,7 +14967,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:3">
       <c r="A674" s="2" t="s">
         <v>1912</v>
       </c>
@@ -14987,7 +14978,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:3">
       <c r="A675" s="3" t="s">
         <v>1915</v>
       </c>
@@ -14998,7 +14989,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:3">
       <c r="A676" s="2" t="s">
         <v>1918</v>
       </c>
@@ -15009,7 +15000,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:3">
       <c r="A677" s="3" t="s">
         <v>1921</v>
       </c>
@@ -15020,7 +15011,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:3">
       <c r="A678" s="2" t="s">
         <v>1924</v>
       </c>
@@ -15031,7 +15022,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:3">
       <c r="A679" s="3" t="s">
         <v>1927</v>
       </c>
@@ -15042,7 +15033,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:3">
       <c r="A680" s="2" t="s">
         <v>1930</v>
       </c>
@@ -15053,7 +15044,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:3">
       <c r="A681" s="3" t="s">
         <v>1933</v>
       </c>
@@ -15064,7 +15055,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:3">
       <c r="A682" s="2" t="s">
         <v>1936</v>
       </c>
@@ -15075,1599 +15066,1588 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A683" s="3" t="s">
+    <row r="683" spans="1:3">
+      <c r="A683" s="2" t="s">
         <v>1939</v>
       </c>
-      <c r="B683" s="3" t="s">
+      <c r="B683" s="2" t="s">
         <v>1940</v>
       </c>
-      <c r="C683" s="3" t="s">
+      <c r="C683" s="2" t="s">
         <v>1941</v>
       </c>
     </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A684" s="2" t="s">
+    <row r="684" spans="1:3">
+      <c r="A684" s="3" t="s">
         <v>1942</v>
       </c>
-      <c r="B684" s="2" t="s">
+      <c r="B684" s="3" t="s">
         <v>1943</v>
       </c>
-      <c r="C684" s="2" t="s">
+      <c r="C684" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3">
+      <c r="A685" s="2" t="s">
         <v>1944</v>
       </c>
-    </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A685" s="3" t="s">
+      <c r="B685" s="2" t="s">
         <v>1945</v>
       </c>
-      <c r="B685" s="3" t="s">
+      <c r="C685" s="2" t="s">
         <v>1946</v>
       </c>
-      <c r="C685" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A686" s="2" t="s">
+    </row>
+    <row r="686" spans="1:3">
+      <c r="A686" s="3" t="s">
         <v>1947</v>
       </c>
-      <c r="B686" s="2" t="s">
+      <c r="B686" s="3" t="s">
         <v>1948</v>
       </c>
-      <c r="C686" s="2" t="s">
+      <c r="C686" s="3" t="s">
         <v>1949</v>
       </c>
     </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A687" s="3" t="s">
+    <row r="687" spans="1:3">
+      <c r="A687" s="2" t="s">
         <v>1950</v>
       </c>
-      <c r="B687" s="3" t="s">
+      <c r="B687" s="2" t="s">
         <v>1951</v>
       </c>
-      <c r="C687" s="3" t="s">
+      <c r="C687" s="2" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3">
+      <c r="A688" s="3" t="s">
         <v>1952</v>
       </c>
-    </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A688" s="2" t="s">
+      <c r="B688" s="3" t="s">
         <v>1953</v>
       </c>
-      <c r="B688" s="2" t="s">
+      <c r="C688" s="3" t="s">
         <v>1954</v>
       </c>
-      <c r="C688" s="2" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A689" s="3" t="s">
+    </row>
+    <row r="689" spans="1:3">
+      <c r="A689" s="2" t="s">
         <v>1955</v>
       </c>
-      <c r="B689" s="3" t="s">
+      <c r="B689" s="2" t="s">
         <v>1956</v>
       </c>
-      <c r="C689" s="3" t="s">
+      <c r="C689" s="2" t="s">
         <v>1957</v>
       </c>
     </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A690" s="2" t="s">
+    <row r="690" spans="1:3">
+      <c r="A690" s="3" t="s">
         <v>1958</v>
       </c>
-      <c r="B690" s="2" t="s">
+      <c r="B690" s="3" t="s">
         <v>1959</v>
       </c>
-      <c r="C690" s="2" t="s">
+      <c r="C690" s="3" t="s">
         <v>1960</v>
       </c>
     </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A691" s="3" t="s">
+    <row r="691" spans="1:3">
+      <c r="A691" s="2" t="s">
         <v>1961</v>
       </c>
-      <c r="B691" s="3" t="s">
+      <c r="B691" s="2" t="s">
         <v>1962</v>
       </c>
-      <c r="C691" s="3" t="s">
+      <c r="C691" s="2" t="s">
         <v>1963</v>
       </c>
     </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A692" s="2" t="s">
+    <row r="692" spans="1:3">
+      <c r="A692" s="3" t="s">
         <v>1964</v>
       </c>
-      <c r="B692" s="2" t="s">
+      <c r="B692" s="3" t="s">
         <v>1965</v>
       </c>
-      <c r="C692" s="2" t="s">
+      <c r="C692" s="3" t="s">
         <v>1966</v>
       </c>
     </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A693" s="3" t="s">
+    <row r="693" spans="1:3">
+      <c r="A693" s="2" t="s">
         <v>1967</v>
       </c>
-      <c r="B693" s="3" t="s">
+      <c r="B693" s="2" t="s">
         <v>1968</v>
       </c>
-      <c r="C693" s="3" t="s">
+      <c r="C693" s="2" t="s">
         <v>1969</v>
       </c>
     </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A694" s="2" t="s">
+    <row r="694" spans="1:3">
+      <c r="A694" s="3" t="s">
         <v>1970</v>
       </c>
-      <c r="B694" s="2" t="s">
+      <c r="B694" s="3" t="s">
         <v>1971</v>
       </c>
-      <c r="C694" s="2" t="s">
+      <c r="C694" s="3" t="s">
         <v>1972</v>
       </c>
     </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A695" s="3" t="s">
+    <row r="695" spans="1:3">
+      <c r="A695" s="2" t="s">
         <v>1973</v>
       </c>
-      <c r="B695" s="3" t="s">
+      <c r="B695" s="2" t="s">
         <v>1974</v>
       </c>
-      <c r="C695" s="3" t="s">
+      <c r="C695" s="2" t="s">
         <v>1975</v>
       </c>
     </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A696" s="2" t="s">
+    <row r="696" spans="1:3">
+      <c r="A696" s="3" t="s">
         <v>1976</v>
       </c>
-      <c r="B696" s="2" t="s">
+      <c r="B696" s="3" t="s">
         <v>1977</v>
       </c>
-      <c r="C696" s="2" t="s">
+      <c r="C696" s="3" t="s">
         <v>1978</v>
       </c>
     </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A697" s="3" t="s">
+    <row r="697" spans="1:3">
+      <c r="A697" s="2" t="s">
         <v>1979</v>
       </c>
-      <c r="B697" s="3" t="s">
+      <c r="B697" s="4" t="s">
         <v>1980</v>
       </c>
-      <c r="C697" s="3" t="s">
+      <c r="C697" s="2" t="s">
         <v>1981</v>
       </c>
     </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A698" s="2" t="s">
+    <row r="698" spans="1:3">
+      <c r="A698" s="3" t="s">
         <v>1982</v>
       </c>
-      <c r="B698" s="4" t="s">
+      <c r="B698" s="3" t="s">
         <v>1983</v>
       </c>
-      <c r="C698" s="2" t="s">
+      <c r="C698" s="3" t="s">
         <v>1984</v>
       </c>
     </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A699" s="3" t="s">
+    <row r="699" spans="1:3">
+      <c r="A699" s="2" t="s">
         <v>1985</v>
       </c>
-      <c r="B699" s="3" t="s">
+      <c r="B699" s="2" t="s">
         <v>1986</v>
       </c>
-      <c r="C699" s="3" t="s">
+      <c r="C699" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3">
+      <c r="A700" s="3" t="s">
         <v>1987</v>
       </c>
-    </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A700" s="2" t="s">
+      <c r="B700" s="3" t="s">
         <v>1988</v>
       </c>
-      <c r="B700" s="2" t="s">
+      <c r="C700" s="3" t="s">
         <v>1989</v>
       </c>
-      <c r="C700" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A701" s="3" t="s">
+    </row>
+    <row r="701" spans="1:3">
+      <c r="A701" s="2" t="s">
         <v>1990</v>
       </c>
-      <c r="B701" s="3" t="s">
+      <c r="B701" s="2" t="s">
         <v>1991</v>
       </c>
-      <c r="C701" s="3" t="s">
+      <c r="C701" s="2" t="s">
         <v>1992</v>
       </c>
     </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A702" s="2" t="s">
+    <row r="702" spans="1:3">
+      <c r="A702" s="3" t="s">
         <v>1993</v>
       </c>
-      <c r="B702" s="2" t="s">
+      <c r="B702" s="3" t="s">
         <v>1994</v>
       </c>
-      <c r="C702" s="2" t="s">
+      <c r="C702" s="3" t="s">
         <v>1995</v>
       </c>
     </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A703" s="3" t="s">
+    <row r="703" spans="1:3">
+      <c r="A703" s="2" t="s">
         <v>1996</v>
       </c>
-      <c r="B703" s="3" t="s">
+      <c r="B703" s="2" t="s">
         <v>1997</v>
       </c>
-      <c r="C703" s="3" t="s">
+      <c r="C703" s="2" t="s">
         <v>1998</v>
       </c>
     </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A704" s="2" t="s">
+    <row r="704" spans="1:3">
+      <c r="A704" s="3" t="s">
         <v>1999</v>
       </c>
-      <c r="B704" s="2" t="s">
+      <c r="B704" s="3" t="s">
         <v>2000</v>
       </c>
-      <c r="C704" s="2" t="s">
+      <c r="C704" s="3" t="s">
         <v>2001</v>
       </c>
     </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A705" s="3" t="s">
+    <row r="705" spans="1:3">
+      <c r="A705" s="2" t="s">
         <v>2002</v>
       </c>
-      <c r="B705" s="3" t="s">
+      <c r="B705" s="2" t="s">
         <v>2003</v>
       </c>
-      <c r="C705" s="3" t="s">
+      <c r="C705" s="2" t="s">
         <v>2004</v>
       </c>
     </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A706" s="2" t="s">
+    <row r="706" spans="1:3">
+      <c r="A706" s="3" t="s">
         <v>2005</v>
       </c>
-      <c r="B706" s="2" t="s">
+      <c r="B706" s="3" t="s">
         <v>2006</v>
       </c>
-      <c r="C706" s="2" t="s">
+      <c r="C706" s="3" t="s">
         <v>2007</v>
       </c>
     </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A707" s="3" t="s">
+    <row r="707" spans="1:3">
+      <c r="A707" s="2" t="s">
         <v>2008</v>
       </c>
-      <c r="B707" s="3" t="s">
+      <c r="B707" s="2" t="s">
         <v>2009</v>
       </c>
-      <c r="C707" s="3" t="s">
+      <c r="C707" s="2" t="s">
         <v>2010</v>
       </c>
     </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A708" s="2" t="s">
+    <row r="708" spans="1:3">
+      <c r="A708" s="3" t="s">
         <v>2011</v>
       </c>
-      <c r="B708" s="2" t="s">
+      <c r="B708" s="3" t="s">
         <v>2012</v>
       </c>
-      <c r="C708" s="2" t="s">
+      <c r="C708" s="3" t="s">
         <v>2013</v>
       </c>
     </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A709" s="3" t="s">
+    <row r="709" spans="1:3">
+      <c r="A709" s="2" t="s">
         <v>2014</v>
       </c>
-      <c r="B709" s="3" t="s">
+      <c r="B709" s="2" t="s">
         <v>2015</v>
       </c>
-      <c r="C709" s="3" t="s">
+      <c r="C709" s="2" t="s">
         <v>2016</v>
       </c>
     </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A710" s="2" t="s">
+    <row r="710" spans="1:3">
+      <c r="A710" s="3" t="s">
         <v>2017</v>
       </c>
-      <c r="B710" s="2" t="s">
+      <c r="B710" s="3" t="s">
         <v>2018</v>
       </c>
-      <c r="C710" s="2" t="s">
+      <c r="C710" s="3" t="s">
         <v>2019</v>
       </c>
     </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A711" s="3" t="s">
+    <row r="711" spans="1:3">
+      <c r="A711" s="2" t="s">
         <v>2020</v>
       </c>
-      <c r="B711" s="3" t="s">
+      <c r="B711" s="2" t="s">
         <v>2021</v>
       </c>
-      <c r="C711" s="3" t="s">
+      <c r="C711" s="2" t="s">
         <v>2022</v>
       </c>
     </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A712" s="2" t="s">
+    <row r="712" spans="1:3">
+      <c r="A712" s="3" t="s">
         <v>2023</v>
       </c>
-      <c r="B712" s="2" t="s">
+      <c r="B712" s="3" t="s">
         <v>2024</v>
       </c>
-      <c r="C712" s="2" t="s">
+      <c r="C712" s="3" t="s">
         <v>2025</v>
       </c>
     </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A713" s="3" t="s">
+    <row r="713" spans="1:3">
+      <c r="A713" s="2" t="s">
         <v>2026</v>
       </c>
-      <c r="B713" s="3" t="s">
+      <c r="B713" s="2" t="s">
         <v>2027</v>
       </c>
-      <c r="C713" s="3" t="s">
+      <c r="C713" s="2" t="s">
         <v>2028</v>
       </c>
     </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A714" s="2" t="s">
+    <row r="714" spans="1:3">
+      <c r="A714" s="3" t="s">
         <v>2029</v>
       </c>
-      <c r="B714" s="2" t="s">
+      <c r="B714" s="3" t="s">
         <v>2030</v>
       </c>
-      <c r="C714" s="2" t="s">
+      <c r="C714" s="3" t="s">
         <v>2031</v>
       </c>
     </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A715" s="3" t="s">
+    <row r="715" spans="1:3">
+      <c r="A715" s="2" t="s">
         <v>2032</v>
       </c>
-      <c r="B715" s="3" t="s">
+      <c r="B715" s="2" t="s">
         <v>2033</v>
       </c>
-      <c r="C715" s="3" t="s">
+      <c r="C715" s="2" t="s">
         <v>2034</v>
       </c>
     </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A716" s="2" t="s">
+    <row r="716" spans="1:3">
+      <c r="A716" s="3" t="s">
         <v>2035</v>
       </c>
-      <c r="B716" s="2" t="s">
+      <c r="B716" s="3" t="s">
         <v>2036</v>
       </c>
-      <c r="C716" s="2" t="s">
+      <c r="C716" s="3" t="s">
         <v>2037</v>
       </c>
     </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A717" s="3" t="s">
+    <row r="717" spans="1:3">
+      <c r="A717" s="2" t="s">
         <v>2038</v>
       </c>
-      <c r="B717" s="3" t="s">
+      <c r="B717" s="2" t="s">
         <v>2039</v>
       </c>
-      <c r="C717" s="3" t="s">
+      <c r="C717" s="2" t="s">
         <v>2040</v>
       </c>
     </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A718" s="2" t="s">
+    <row r="718" spans="1:3">
+      <c r="A718" s="3" t="s">
         <v>2041</v>
       </c>
-      <c r="B718" s="2" t="s">
+      <c r="B718" s="3" t="s">
         <v>2042</v>
       </c>
-      <c r="C718" s="2" t="s">
+      <c r="C718" s="3" t="s">
         <v>2043</v>
       </c>
     </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A719" s="3" t="s">
+    <row r="719" spans="1:3">
+      <c r="A719" s="2" t="s">
         <v>2044</v>
       </c>
-      <c r="B719" s="3" t="s">
+      <c r="B719" s="2" t="s">
         <v>2045</v>
       </c>
-      <c r="C719" s="3" t="s">
+      <c r="C719" s="2" t="s">
         <v>2046</v>
       </c>
     </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A720" s="2" t="s">
+    <row r="720" spans="1:3">
+      <c r="A720" s="3" t="s">
         <v>2047</v>
       </c>
-      <c r="B720" s="2" t="s">
+      <c r="B720" s="3" t="s">
         <v>2048</v>
       </c>
-      <c r="C720" s="2" t="s">
+      <c r="C720" s="3" t="s">
         <v>2049</v>
       </c>
     </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A721" s="3" t="s">
+    <row r="721" spans="1:3">
+      <c r="A721" s="2" t="s">
         <v>2050</v>
       </c>
-      <c r="B721" s="3" t="s">
+      <c r="B721" s="2" t="s">
         <v>2051</v>
       </c>
-      <c r="C721" s="3" t="s">
+      <c r="C721" s="2" t="s">
         <v>2052</v>
       </c>
     </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A722" s="2" t="s">
+    <row r="722" spans="1:3">
+      <c r="A722" s="3" t="s">
         <v>2053</v>
       </c>
-      <c r="B722" s="2" t="s">
+      <c r="B722" s="3" t="s">
         <v>2054</v>
       </c>
-      <c r="C722" s="2" t="s">
+      <c r="C722" s="3" t="s">
         <v>2055</v>
       </c>
     </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A723" s="3" t="s">
+    <row r="723" spans="1:3">
+      <c r="A723" s="2" t="s">
         <v>2056</v>
       </c>
-      <c r="B723" s="3" t="s">
+      <c r="B723" s="2" t="s">
         <v>2057</v>
       </c>
-      <c r="C723" s="3" t="s">
+      <c r="C723" s="2" t="s">
         <v>2058</v>
       </c>
     </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A724" s="2" t="s">
+    <row r="724" spans="1:3">
+      <c r="A724" s="3" t="s">
         <v>2059</v>
       </c>
-      <c r="B724" s="2" t="s">
+      <c r="B724" s="3" t="s">
         <v>2060</v>
       </c>
-      <c r="C724" s="2" t="s">
+      <c r="C724" s="3" t="s">
         <v>2061</v>
       </c>
     </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A725" s="3" t="s">
+    <row r="725" spans="1:3">
+      <c r="A725" s="2" t="s">
         <v>2062</v>
       </c>
-      <c r="B725" s="3" t="s">
+      <c r="B725" s="2" t="s">
         <v>2063</v>
       </c>
-      <c r="C725" s="3" t="s">
+      <c r="C725" s="2" t="s">
         <v>2064</v>
       </c>
     </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A726" s="2" t="s">
+    <row r="726" spans="1:3">
+      <c r="A726" s="3" t="s">
         <v>2065</v>
       </c>
-      <c r="B726" s="2" t="s">
+      <c r="B726" s="3" t="s">
         <v>2066</v>
       </c>
-      <c r="C726" s="2" t="s">
+      <c r="C726" s="3" t="s">
         <v>2067</v>
       </c>
     </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A727" s="3" t="s">
+    <row r="727" spans="1:3">
+      <c r="A727" s="2" t="s">
         <v>2068</v>
       </c>
-      <c r="B727" s="3" t="s">
+      <c r="B727" s="2" t="s">
         <v>2069</v>
       </c>
-      <c r="C727" s="3" t="s">
+      <c r="C727" s="2" t="s">
         <v>2070</v>
       </c>
     </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A728" s="2" t="s">
+    <row r="728" spans="1:3">
+      <c r="A728" s="3" t="s">
         <v>2071</v>
       </c>
-      <c r="B728" s="2" t="s">
+      <c r="B728" s="3" t="s">
         <v>2072</v>
       </c>
-      <c r="C728" s="2" t="s">
+      <c r="C728" s="3" t="s">
         <v>2073</v>
       </c>
     </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A729" s="3" t="s">
+    <row r="729" spans="1:3">
+      <c r="A729" s="2" t="s">
         <v>2074</v>
       </c>
-      <c r="B729" s="3" t="s">
+      <c r="B729" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="C729" s="3" t="s">
+      <c r="C729" s="2" t="s">
         <v>2076</v>
       </c>
     </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A730" s="2" t="s">
+    <row r="730" spans="1:3">
+      <c r="A730" s="3" t="s">
         <v>2077</v>
       </c>
-      <c r="B730" s="2" t="s">
+      <c r="B730" s="3" t="s">
         <v>2078</v>
       </c>
-      <c r="C730" s="2" t="s">
+      <c r="C730" s="3" t="s">
         <v>2079</v>
       </c>
     </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A731" s="3" t="s">
+    <row r="731" spans="1:3">
+      <c r="A731" s="2" t="s">
         <v>2080</v>
       </c>
-      <c r="B731" s="3" t="s">
+      <c r="B731" s="2" t="s">
         <v>2081</v>
       </c>
-      <c r="C731" s="3" t="s">
+      <c r="C731" s="2" t="s">
         <v>2082</v>
       </c>
     </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A732" s="2" t="s">
+    <row r="732" spans="1:3">
+      <c r="A732" s="3" t="s">
         <v>2083</v>
       </c>
-      <c r="B732" s="2" t="s">
+      <c r="B732" s="3" t="s">
         <v>2084</v>
       </c>
-      <c r="C732" s="2" t="s">
+      <c r="C732" s="3" t="s">
         <v>2085</v>
       </c>
     </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A733" s="3" t="s">
+    <row r="733" spans="1:3">
+      <c r="A733" s="2" t="s">
         <v>2086</v>
       </c>
-      <c r="B733" s="3" t="s">
+      <c r="B733" s="2" t="s">
         <v>2087</v>
       </c>
-      <c r="C733" s="3" t="s">
+      <c r="C733" s="2" t="s">
         <v>2088</v>
       </c>
     </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A734" s="2" t="s">
+    <row r="734" spans="1:3">
+      <c r="A734" s="3" t="s">
         <v>2089</v>
       </c>
-      <c r="B734" s="2" t="s">
+      <c r="B734" s="3" t="s">
         <v>2090</v>
       </c>
-      <c r="C734" s="2" t="s">
+      <c r="C734" s="3" t="s">
         <v>2091</v>
       </c>
     </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A735" s="3" t="s">
+    <row r="735" spans="1:3">
+      <c r="A735" s="2" t="s">
         <v>2092</v>
       </c>
-      <c r="B735" s="3" t="s">
+      <c r="B735" s="2" t="s">
         <v>2093</v>
       </c>
-      <c r="C735" s="3" t="s">
+      <c r="C735" s="2" t="s">
         <v>2094</v>
       </c>
     </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A736" s="2" t="s">
+    <row r="736" spans="1:3">
+      <c r="A736" s="3" t="s">
         <v>2095</v>
       </c>
-      <c r="B736" s="2" t="s">
+      <c r="B736" s="3" t="s">
         <v>2096</v>
       </c>
-      <c r="C736" s="2" t="s">
+      <c r="C736" s="3" t="s">
         <v>2097</v>
       </c>
     </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A737" s="3" t="s">
+    <row r="737" spans="1:3">
+      <c r="A737" s="2" t="s">
         <v>2098</v>
       </c>
-      <c r="B737" s="3" t="s">
+      <c r="B737" s="2" t="s">
         <v>2099</v>
       </c>
-      <c r="C737" s="3" t="s">
+      <c r="C737" s="2" t="s">
         <v>2100</v>
       </c>
     </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A738" s="2" t="s">
+    <row r="738" spans="1:3">
+      <c r="A738" s="3" t="s">
         <v>2101</v>
       </c>
-      <c r="B738" s="2" t="s">
+      <c r="B738" s="3" t="s">
         <v>2102</v>
       </c>
-      <c r="C738" s="2" t="s">
+      <c r="C738" s="3" t="s">
         <v>2103</v>
       </c>
     </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A739" s="3" t="s">
+    <row r="739" spans="1:3">
+      <c r="A739" s="2" t="s">
         <v>2104</v>
       </c>
-      <c r="B739" s="3" t="s">
+      <c r="B739" s="2" t="s">
         <v>2105</v>
       </c>
-      <c r="C739" s="3" t="s">
+      <c r="C739" s="2" t="s">
         <v>2106</v>
       </c>
     </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A740" s="2" t="s">
+    <row r="740" spans="1:3">
+      <c r="A740" s="3" t="s">
         <v>2107</v>
       </c>
-      <c r="B740" s="2" t="s">
+      <c r="B740" s="3" t="s">
         <v>2108</v>
       </c>
-      <c r="C740" s="2" t="s">
+      <c r="C740" s="3" t="s">
         <v>2109</v>
       </c>
     </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A741" s="3" t="s">
+    <row r="741" spans="1:3">
+      <c r="A741" s="2" t="s">
         <v>2110</v>
       </c>
-      <c r="B741" s="3" t="s">
+      <c r="B741" s="2" t="s">
         <v>2111</v>
       </c>
-      <c r="C741" s="3" t="s">
+      <c r="C741" s="2" t="s">
         <v>2112</v>
       </c>
     </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A742" s="2" t="s">
+    <row r="742" spans="1:3">
+      <c r="A742" s="3" t="s">
         <v>2113</v>
       </c>
-      <c r="B742" s="2" t="s">
+      <c r="B742" s="3" t="s">
         <v>2114</v>
       </c>
-      <c r="C742" s="2" t="s">
+      <c r="C742" s="3" t="s">
         <v>2115</v>
       </c>
     </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A743" s="3" t="s">
+    <row r="743" spans="1:3">
+      <c r="A743" s="2" t="s">
         <v>2116</v>
       </c>
-      <c r="B743" s="3" t="s">
+      <c r="B743" s="2" t="s">
         <v>2117</v>
       </c>
-      <c r="C743" s="3" t="s">
+      <c r="C743" s="2" t="s">
         <v>2118</v>
       </c>
     </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A744" s="2" t="s">
+    <row r="744" spans="1:3">
+      <c r="A744" s="3" t="s">
         <v>2119</v>
       </c>
-      <c r="B744" s="2" t="s">
+      <c r="B744" s="3" t="s">
         <v>2120</v>
       </c>
-      <c r="C744" s="2" t="s">
+      <c r="C744" s="3" t="s">
         <v>2121</v>
       </c>
     </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A745" s="3" t="s">
+    <row r="745" spans="1:3">
+      <c r="A745" s="2" t="s">
         <v>2122</v>
       </c>
-      <c r="B745" s="3" t="s">
+      <c r="B745" s="2" t="s">
         <v>2123</v>
       </c>
-      <c r="C745" s="3" t="s">
+      <c r="C745" s="2" t="s">
         <v>2124</v>
       </c>
     </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A746" s="2" t="s">
+    <row r="746" spans="1:3">
+      <c r="A746" s="3" t="s">
         <v>2125</v>
       </c>
-      <c r="B746" s="2" t="s">
+      <c r="B746" s="3" t="s">
         <v>2126</v>
       </c>
-      <c r="C746" s="2" t="s">
+      <c r="C746" s="3" t="s">
         <v>2127</v>
       </c>
     </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A747" s="3" t="s">
+    <row r="747" spans="1:3">
+      <c r="A747" s="2" t="s">
         <v>2128</v>
       </c>
-      <c r="B747" s="3" t="s">
+      <c r="B747" s="2" t="s">
         <v>2129</v>
       </c>
-      <c r="C747" s="3" t="s">
+      <c r="C747" s="2" t="s">
         <v>2130</v>
       </c>
     </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A748" s="2" t="s">
+    <row r="748" spans="1:3">
+      <c r="A748" s="3" t="s">
         <v>2131</v>
       </c>
-      <c r="B748" s="2" t="s">
+      <c r="B748" s="3" t="s">
         <v>2132</v>
       </c>
-      <c r="C748" s="2" t="s">
+      <c r="C748" s="3" t="s">
         <v>2133</v>
       </c>
     </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A749" s="3" t="s">
+    <row r="749" spans="1:3">
+      <c r="A749" s="2" t="s">
         <v>2134</v>
       </c>
-      <c r="B749" s="3" t="s">
+      <c r="B749" s="2" t="s">
         <v>2135</v>
       </c>
-      <c r="C749" s="3" t="s">
+      <c r="C749" s="2" t="s">
         <v>2136</v>
       </c>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A750" s="2" t="s">
+    <row r="750" spans="1:3">
+      <c r="A750" s="3" t="s">
         <v>2137</v>
       </c>
-      <c r="B750" s="2" t="s">
+      <c r="B750" s="3" t="s">
         <v>2138</v>
       </c>
-      <c r="C750" s="2" t="s">
+      <c r="C750" s="3" t="s">
         <v>2139</v>
       </c>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A751" s="3" t="s">
+    <row r="751" spans="1:3">
+      <c r="A751" s="2" t="s">
         <v>2140</v>
       </c>
-      <c r="B751" s="3" t="s">
+      <c r="B751" s="2" t="s">
         <v>2141</v>
       </c>
-      <c r="C751" s="3" t="s">
+      <c r="C751" s="2" t="s">
         <v>2142</v>
       </c>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A752" s="2" t="s">
+    <row r="752" spans="1:3">
+      <c r="A752" s="3" t="s">
         <v>2143</v>
       </c>
-      <c r="B752" s="2" t="s">
+      <c r="B752" s="3" t="s">
         <v>2144</v>
       </c>
-      <c r="C752" s="2" t="s">
+      <c r="C752" s="3" t="s">
         <v>2145</v>
       </c>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A753" s="3" t="s">
+    <row r="753" spans="1:3">
+      <c r="A753" s="2" t="s">
         <v>2146</v>
       </c>
-      <c r="B753" s="3" t="s">
+      <c r="B753" s="4" t="s">
         <v>2147</v>
       </c>
-      <c r="C753" s="3" t="s">
+      <c r="C753" s="2" t="s">
         <v>2148</v>
       </c>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A754" s="2" t="s">
+    <row r="754" spans="1:3">
+      <c r="A754" s="3" t="s">
         <v>2149</v>
       </c>
-      <c r="B754" s="4" t="s">
+      <c r="B754" s="3" t="s">
         <v>2150</v>
       </c>
-      <c r="C754" s="2" t="s">
+      <c r="C754" s="3" t="s">
         <v>2151</v>
       </c>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A755" s="3" t="s">
+    <row r="755" spans="1:3">
+      <c r="A755" s="2" t="s">
         <v>2152</v>
       </c>
-      <c r="B755" s="3" t="s">
+      <c r="B755" s="2" t="s">
         <v>2153</v>
       </c>
-      <c r="C755" s="3" t="s">
+      <c r="C755" s="2" t="s">
         <v>2154</v>
       </c>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A756" s="2" t="s">
+    <row r="756" spans="1:3">
+      <c r="A756" s="3" t="s">
         <v>2155</v>
       </c>
-      <c r="B756" s="2" t="s">
+      <c r="B756" s="3" t="s">
         <v>2156</v>
       </c>
-      <c r="C756" s="2" t="s">
+      <c r="C756" s="3" t="s">
         <v>2157</v>
       </c>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A757" s="3" t="s">
+    <row r="757" spans="1:3">
+      <c r="A757" s="2" t="s">
         <v>2158</v>
       </c>
-      <c r="B757" s="3" t="s">
+      <c r="B757" s="2" t="s">
         <v>2159</v>
       </c>
-      <c r="C757" s="3" t="s">
+      <c r="C757" s="2" t="s">
         <v>2160</v>
       </c>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A758" s="2" t="s">
+    <row r="758" spans="1:3">
+      <c r="A758" s="3" t="s">
         <v>2161</v>
       </c>
-      <c r="B758" s="2" t="s">
+      <c r="B758" s="3" t="s">
         <v>2162</v>
       </c>
-      <c r="C758" s="2" t="s">
+      <c r="C758" s="3" t="s">
         <v>2163</v>
       </c>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A759" s="3" t="s">
+    <row r="759" spans="1:3">
+      <c r="A759" s="2" t="s">
         <v>2164</v>
       </c>
-      <c r="B759" s="3" t="s">
+      <c r="B759" s="2" t="s">
         <v>2165</v>
       </c>
-      <c r="C759" s="3" t="s">
+      <c r="C759" s="2" t="s">
         <v>2166</v>
       </c>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A760" s="2" t="s">
+    <row r="760" spans="1:3">
+      <c r="A760" s="3" t="s">
         <v>2167</v>
       </c>
-      <c r="B760" s="2" t="s">
+      <c r="B760" s="3" t="s">
         <v>2168</v>
       </c>
-      <c r="C760" s="2" t="s">
+      <c r="C760" s="3" t="s">
         <v>2169</v>
       </c>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A761" s="3" t="s">
+    <row r="761" spans="1:3">
+      <c r="A761" s="2" t="s">
         <v>2170</v>
       </c>
-      <c r="B761" s="3" t="s">
+      <c r="B761" s="2" t="s">
         <v>2171</v>
       </c>
-      <c r="C761" s="3" t="s">
+      <c r="C761" s="2" t="s">
         <v>2172</v>
       </c>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A762" s="2" t="s">
+    <row r="762" spans="1:3">
+      <c r="A762" s="3" t="s">
         <v>2173</v>
       </c>
-      <c r="B762" s="2" t="s">
+      <c r="B762" s="3" t="s">
         <v>2174</v>
       </c>
-      <c r="C762" s="2" t="s">
+      <c r="C762" s="3" t="s">
         <v>2175</v>
       </c>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A763" s="3" t="s">
+    <row r="763" spans="1:3">
+      <c r="A763" s="2" t="s">
         <v>2176</v>
       </c>
-      <c r="B763" s="3" t="s">
+      <c r="B763" s="2" t="s">
         <v>2177</v>
       </c>
-      <c r="C763" s="3" t="s">
+      <c r="C763" s="2" t="s">
         <v>2178</v>
       </c>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A764" s="2" t="s">
+    <row r="764" spans="1:3">
+      <c r="A764" s="3" t="s">
         <v>2179</v>
       </c>
-      <c r="B764" s="2" t="s">
+      <c r="B764" s="3" t="s">
         <v>2180</v>
       </c>
-      <c r="C764" s="2" t="s">
+      <c r="C764" s="3" t="s">
         <v>2181</v>
       </c>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A765" s="3" t="s">
+    <row r="765" spans="1:3">
+      <c r="A765" s="2" t="s">
         <v>2182</v>
       </c>
-      <c r="B765" s="3" t="s">
+      <c r="B765" s="2" t="s">
         <v>2183</v>
       </c>
-      <c r="C765" s="3" t="s">
+      <c r="C765" s="2" t="s">
         <v>2184</v>
       </c>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A766" s="2" t="s">
+    <row r="766" spans="1:3">
+      <c r="A766" s="3" t="s">
         <v>2185</v>
       </c>
-      <c r="B766" s="2" t="s">
+      <c r="B766" s="3" t="s">
         <v>2186</v>
       </c>
-      <c r="C766" s="2" t="s">
+      <c r="C766" s="3" t="s">
         <v>2187</v>
       </c>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A767" s="3" t="s">
+    <row r="767" spans="1:3">
+      <c r="A767" s="2" t="s">
         <v>2188</v>
       </c>
-      <c r="B767" s="3" t="s">
+      <c r="B767" s="2" t="s">
         <v>2189</v>
       </c>
-      <c r="C767" s="3" t="s">
+      <c r="C767" s="2" t="s">
         <v>2190</v>
       </c>
     </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A768" s="2" t="s">
+    <row r="768" spans="1:3">
+      <c r="A768" s="3" t="s">
         <v>2191</v>
       </c>
-      <c r="B768" s="2" t="s">
+      <c r="B768" s="3" t="s">
         <v>2192</v>
       </c>
-      <c r="C768" s="2" t="s">
+      <c r="C768" s="3" t="s">
         <v>2193</v>
       </c>
     </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A769" s="3" t="s">
+    <row r="769" spans="1:3">
+      <c r="A769" s="2" t="s">
         <v>2194</v>
       </c>
-      <c r="B769" s="3" t="s">
+      <c r="B769" s="2" t="s">
         <v>2195</v>
       </c>
-      <c r="C769" s="3" t="s">
+      <c r="C769" s="2" t="s">
         <v>2196</v>
       </c>
     </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A770" s="2" t="s">
+    <row r="770" spans="1:3">
+      <c r="A770" s="3" t="s">
         <v>2197</v>
       </c>
-      <c r="B770" s="2" t="s">
+      <c r="B770" s="3" t="s">
         <v>2198</v>
       </c>
-      <c r="C770" s="2" t="s">
+      <c r="C770" s="3" t="s">
         <v>2199</v>
       </c>
     </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A771" s="3" t="s">
+    <row r="771" spans="1:3">
+      <c r="A771" s="2" t="s">
         <v>2200</v>
       </c>
-      <c r="B771" s="3" t="s">
+      <c r="B771" s="2" t="s">
         <v>2201</v>
       </c>
-      <c r="C771" s="3" t="s">
+      <c r="C771" s="2" t="s">
         <v>2202</v>
       </c>
     </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A772" s="2" t="s">
+    <row r="772" spans="1:3">
+      <c r="A772" s="3" t="s">
         <v>2203</v>
       </c>
-      <c r="B772" s="2" t="s">
+      <c r="B772" s="3" t="s">
         <v>2204</v>
       </c>
-      <c r="C772" s="2" t="s">
+      <c r="C772" s="3" t="s">
         <v>2205</v>
       </c>
     </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A773" s="3" t="s">
+    <row r="773" spans="1:3">
+      <c r="A773" s="2" t="s">
         <v>2206</v>
       </c>
-      <c r="B773" s="3" t="s">
+      <c r="B773" s="2" t="s">
         <v>2207</v>
       </c>
-      <c r="C773" s="3" t="s">
+      <c r="C773" s="2" t="s">
         <v>2208</v>
       </c>
     </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A774" s="2" t="s">
+    <row r="774" spans="1:3">
+      <c r="A774" s="3" t="s">
         <v>2209</v>
       </c>
-      <c r="B774" s="2" t="s">
+      <c r="B774" s="3" t="s">
         <v>2210</v>
       </c>
-      <c r="C774" s="2" t="s">
+      <c r="C774" s="3" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3">
+      <c r="A775" s="2" t="s">
         <v>2211</v>
       </c>
-    </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A775" s="3" t="s">
+      <c r="B775" s="2" t="s">
         <v>2212</v>
       </c>
-      <c r="B775" s="3" t="s">
+      <c r="C775" s="2" t="s">
         <v>2213</v>
       </c>
-      <c r="C775" s="3" t="s">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A776" s="2" t="s">
+    </row>
+    <row r="776" spans="1:3">
+      <c r="A776" s="3" t="s">
         <v>2214</v>
       </c>
-      <c r="B776" s="2" t="s">
+      <c r="B776" s="3" t="s">
         <v>2215</v>
       </c>
-      <c r="C776" s="2" t="s">
+      <c r="C776" s="3" t="s">
         <v>2216</v>
       </c>
     </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A777" s="3" t="s">
+    <row r="777" spans="1:3">
+      <c r="A777" s="2" t="s">
         <v>2217</v>
       </c>
-      <c r="B777" s="3" t="s">
+      <c r="B777" s="2" t="s">
         <v>2218</v>
       </c>
-      <c r="C777" s="3" t="s">
+      <c r="C777" s="2" t="s">
         <v>2219</v>
       </c>
     </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A778" s="2" t="s">
+    <row r="778" spans="1:3">
+      <c r="A778" s="3" t="s">
         <v>2220</v>
       </c>
-      <c r="B778" s="2" t="s">
+      <c r="B778" s="3" t="s">
         <v>2221</v>
       </c>
-      <c r="C778" s="2" t="s">
+      <c r="C778" s="3" t="s">
         <v>2222</v>
       </c>
     </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A779" s="3" t="s">
+    <row r="779" spans="1:3">
+      <c r="A779" s="2" t="s">
         <v>2223</v>
       </c>
-      <c r="B779" s="3" t="s">
+      <c r="B779" s="2" t="s">
         <v>2224</v>
       </c>
-      <c r="C779" s="3" t="s">
+      <c r="C779" s="2" t="s">
         <v>2225</v>
       </c>
     </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A780" s="2" t="s">
+    <row r="780" spans="1:3">
+      <c r="A780" s="3" t="s">
         <v>2226</v>
       </c>
-      <c r="B780" s="2" t="s">
+      <c r="B780" s="3" t="s">
         <v>2227</v>
       </c>
-      <c r="C780" s="2" t="s">
+      <c r="C780" s="3" t="s">
         <v>2228</v>
       </c>
     </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A781" s="3" t="s">
+    <row r="781" spans="1:3">
+      <c r="A781" s="2" t="s">
         <v>2229</v>
       </c>
-      <c r="B781" s="3" t="s">
+      <c r="B781" s="2" t="s">
         <v>2230</v>
       </c>
-      <c r="C781" s="3" t="s">
+      <c r="C781" s="2" t="s">
         <v>2231</v>
       </c>
     </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A782" s="2" t="s">
+    <row r="782" spans="1:3">
+      <c r="A782" s="3" t="s">
         <v>2232</v>
       </c>
-      <c r="B782" s="2" t="s">
+      <c r="B782" s="3" t="s">
         <v>2233</v>
       </c>
-      <c r="C782" s="2" t="s">
+      <c r="C782" s="3" t="s">
         <v>2234</v>
       </c>
     </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A783" s="3" t="s">
+    <row r="783" spans="1:3">
+      <c r="A783" s="2" t="s">
         <v>2235</v>
       </c>
-      <c r="B783" s="3" t="s">
+      <c r="B783" s="2" t="s">
         <v>2236</v>
       </c>
-      <c r="C783" s="3" t="s">
+      <c r="C783" s="2" t="s">
         <v>2237</v>
       </c>
     </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A784" s="2" t="s">
+    <row r="784" spans="1:3">
+      <c r="A784" s="3" t="s">
         <v>2238</v>
       </c>
-      <c r="B784" s="2" t="s">
+      <c r="B784" s="3" t="s">
         <v>2239</v>
       </c>
-      <c r="C784" s="2" t="s">
+      <c r="C784" s="3" t="s">
         <v>2240</v>
       </c>
     </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A785" s="3" t="s">
+    <row r="785" spans="1:3">
+      <c r="A785" s="2" t="s">
         <v>2241</v>
       </c>
-      <c r="B785" s="3" t="s">
+      <c r="B785" s="2" t="s">
         <v>2242</v>
       </c>
-      <c r="C785" s="3" t="s">
+      <c r="C785" s="2" t="s">
         <v>2243</v>
       </c>
     </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A786" s="2" t="s">
+    <row r="786" spans="1:3">
+      <c r="A786" s="3" t="s">
         <v>2244</v>
       </c>
-      <c r="B786" s="2" t="s">
+      <c r="B786" s="3" t="s">
         <v>2245</v>
       </c>
-      <c r="C786" s="2" t="s">
+      <c r="C786" s="3" t="s">
         <v>2246</v>
       </c>
     </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A787" s="3" t="s">
+    <row r="787" spans="1:3">
+      <c r="A787" s="2" t="s">
         <v>2247</v>
       </c>
-      <c r="B787" s="3" t="s">
+      <c r="B787" s="2" t="s">
         <v>2248</v>
       </c>
-      <c r="C787" s="3" t="s">
+      <c r="C787" s="2" t="s">
         <v>2249</v>
       </c>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A788" s="2" t="s">
+    <row r="788" spans="1:3">
+      <c r="A788" s="3" t="s">
         <v>2250</v>
       </c>
-      <c r="B788" s="2" t="s">
+      <c r="B788" s="3" t="s">
         <v>2251</v>
       </c>
-      <c r="C788" s="2" t="s">
+      <c r="C788" s="3" t="s">
         <v>2252</v>
       </c>
     </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A789" s="3" t="s">
+    <row r="789" spans="1:3">
+      <c r="A789" s="2" t="s">
         <v>2253</v>
       </c>
-      <c r="B789" s="3" t="s">
+      <c r="B789" s="2" t="s">
         <v>2254</v>
       </c>
-      <c r="C789" s="3" t="s">
+      <c r="C789" s="2" t="s">
         <v>2255</v>
       </c>
     </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A790" s="2" t="s">
+    <row r="790" spans="1:3">
+      <c r="A790" s="3" t="s">
         <v>2256</v>
       </c>
-      <c r="B790" s="2" t="s">
+      <c r="B790" s="3" t="s">
         <v>2257</v>
       </c>
-      <c r="C790" s="2" t="s">
+      <c r="C790" s="3" t="s">
         <v>2258</v>
       </c>
     </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A791" s="3" t="s">
+    <row r="791" spans="1:3">
+      <c r="A791" s="2" t="s">
         <v>2259</v>
       </c>
-      <c r="B791" s="3" t="s">
+      <c r="B791" s="2" t="s">
         <v>2260</v>
       </c>
-      <c r="C791" s="3" t="s">
+      <c r="C791" s="2" t="s">
         <v>2261</v>
       </c>
     </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A792" s="2" t="s">
+    <row r="792" spans="1:3">
+      <c r="A792" s="3" t="s">
         <v>2262</v>
       </c>
-      <c r="B792" s="2" t="s">
+      <c r="B792" s="3" t="s">
         <v>2263</v>
       </c>
-      <c r="C792" s="2" t="s">
+      <c r="C792" s="3" t="s">
         <v>2264</v>
       </c>
     </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A793" s="3" t="s">
+    <row r="793" spans="1:3">
+      <c r="A793" s="2" t="s">
         <v>2265</v>
       </c>
-      <c r="B793" s="3" t="s">
+      <c r="B793" s="2" t="s">
         <v>2266</v>
       </c>
-      <c r="C793" s="3" t="s">
+      <c r="C793" s="2" t="s">
         <v>2267</v>
       </c>
     </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A794" s="2" t="s">
+    <row r="794" spans="1:3">
+      <c r="A794" s="3" t="s">
         <v>2268</v>
       </c>
-      <c r="B794" s="2" t="s">
+      <c r="B794" s="3" t="s">
         <v>2269</v>
       </c>
-      <c r="C794" s="2" t="s">
+      <c r="C794" s="3" t="s">
         <v>2270</v>
       </c>
     </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A795" s="3" t="s">
+    <row r="795" spans="1:3">
+      <c r="A795" s="2" t="s">
         <v>2271</v>
       </c>
-      <c r="B795" s="3" t="s">
+      <c r="B795" s="2" t="s">
         <v>2272</v>
       </c>
-      <c r="C795" s="3" t="s">
+      <c r="C795" s="2" t="s">
         <v>2273</v>
       </c>
     </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A796" s="2" t="s">
+    <row r="796" spans="1:3">
+      <c r="A796" s="3" t="s">
         <v>2274</v>
       </c>
-      <c r="B796" s="2" t="s">
+      <c r="B796" s="3" t="s">
         <v>2275</v>
       </c>
-      <c r="C796" s="2" t="s">
+      <c r="C796" s="3" t="s">
         <v>2276</v>
       </c>
     </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A797" s="3" t="s">
+    <row r="797" spans="1:3">
+      <c r="A797" s="2" t="s">
         <v>2277</v>
       </c>
-      <c r="B797" s="3" t="s">
+      <c r="B797" s="2" t="s">
         <v>2278</v>
       </c>
-      <c r="C797" s="3" t="s">
+      <c r="C797" s="2" t="s">
         <v>2279</v>
       </c>
     </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A798" s="2" t="s">
+    <row r="798" spans="1:3">
+      <c r="A798" s="3" t="s">
         <v>2280</v>
       </c>
-      <c r="B798" s="2" t="s">
+      <c r="B798" s="3" t="s">
         <v>2281</v>
       </c>
-      <c r="C798" s="2" t="s">
+      <c r="C798" s="3" t="s">
         <v>2282</v>
       </c>
     </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A799" s="3" t="s">
+    <row r="799" spans="1:3">
+      <c r="A799" s="2" t="s">
         <v>2283</v>
       </c>
-      <c r="B799" s="3" t="s">
+      <c r="B799" s="2" t="s">
         <v>2284</v>
       </c>
-      <c r="C799" s="3" t="s">
+      <c r="C799" s="2" t="s">
         <v>2285</v>
       </c>
     </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A800" s="2" t="s">
+    <row r="800" spans="1:3">
+      <c r="A800" s="3" t="s">
         <v>2286</v>
       </c>
-      <c r="B800" s="2" t="s">
+      <c r="B800" s="3" t="s">
         <v>2287</v>
       </c>
-      <c r="C800" s="2" t="s">
+      <c r="C800" s="3" t="s">
         <v>2288</v>
       </c>
     </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A801" s="3" t="s">
+    <row r="801" spans="1:3">
+      <c r="A801" s="2" t="s">
         <v>2289</v>
       </c>
-      <c r="B801" s="3" t="s">
+      <c r="B801" s="2" t="s">
         <v>2290</v>
       </c>
-      <c r="C801" s="3" t="s">
+      <c r="C801" s="2" t="s">
         <v>2291</v>
       </c>
     </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A802" s="2" t="s">
+    <row r="802" spans="1:3">
+      <c r="A802" s="3" t="s">
         <v>2292</v>
       </c>
-      <c r="B802" s="2" t="s">
+      <c r="B802" s="3" t="s">
         <v>2293</v>
       </c>
-      <c r="C802" s="2" t="s">
+      <c r="C802" s="3" t="s">
         <v>2294</v>
       </c>
     </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A803" s="3" t="s">
+    <row r="803" spans="1:3">
+      <c r="A803" s="2" t="s">
         <v>2295</v>
       </c>
-      <c r="B803" s="3" t="s">
+      <c r="B803" s="2" t="s">
         <v>2296</v>
       </c>
-      <c r="C803" s="3" t="s">
+      <c r="C803" s="2" t="s">
         <v>2297</v>
       </c>
     </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A804" s="2" t="s">
+    <row r="804" spans="1:3">
+      <c r="A804" s="3" t="s">
         <v>2298</v>
       </c>
-      <c r="B804" s="2" t="s">
+      <c r="B804" s="3" t="s">
         <v>2299</v>
       </c>
-      <c r="C804" s="2" t="s">
+      <c r="C804" s="3" t="s">
         <v>2300</v>
       </c>
     </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A805" s="3" t="s">
+    <row r="805" spans="1:3">
+      <c r="A805" s="2" t="s">
         <v>2301</v>
       </c>
-      <c r="B805" s="3" t="s">
+      <c r="B805" s="2" t="s">
         <v>2302</v>
       </c>
-      <c r="C805" s="3" t="s">
+      <c r="C805" s="2" t="s">
         <v>2303</v>
       </c>
     </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A806" s="2" t="s">
+    <row r="806" spans="1:3">
+      <c r="A806" s="3" t="s">
         <v>2304</v>
       </c>
-      <c r="B806" s="2" t="s">
+      <c r="B806" s="3" t="s">
         <v>2305</v>
       </c>
-      <c r="C806" s="2" t="s">
+      <c r="C806" s="3" t="s">
         <v>2306</v>
       </c>
     </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A807" s="3" t="s">
+    <row r="807" spans="1:3">
+      <c r="A807" s="2" t="s">
         <v>2307</v>
       </c>
-      <c r="B807" s="3" t="s">
+      <c r="B807" s="2" t="s">
         <v>2308</v>
       </c>
-      <c r="C807" s="3" t="s">
+      <c r="C807" s="2" t="s">
         <v>2309</v>
       </c>
     </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A808" s="2" t="s">
+    <row r="808" spans="1:3">
+      <c r="A808" s="3" t="s">
         <v>2310</v>
       </c>
-      <c r="B808" s="2" t="s">
+      <c r="B808" s="3" t="s">
         <v>2311</v>
       </c>
-      <c r="C808" s="2" t="s">
+      <c r="C808" s="3" t="s">
         <v>2312</v>
       </c>
     </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A809" s="3" t="s">
+    <row r="809" spans="1:3">
+      <c r="A809" s="2" t="s">
         <v>2313</v>
       </c>
-      <c r="B809" s="3" t="s">
+      <c r="B809" s="2" t="s">
         <v>2314</v>
       </c>
-      <c r="C809" s="3" t="s">
+      <c r="C809" s="2" t="s">
         <v>2315</v>
       </c>
     </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A810" s="2" t="s">
+    <row r="810" spans="1:3">
+      <c r="A810" s="3" t="s">
         <v>2316</v>
       </c>
-      <c r="B810" s="2" t="s">
+      <c r="B810" s="3" t="s">
         <v>2317</v>
       </c>
-      <c r="C810" s="2" t="s">
+      <c r="C810" s="3" t="s">
         <v>2318</v>
       </c>
     </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A811" s="3" t="s">
+    <row r="811" spans="1:3">
+      <c r="A811" s="2" t="s">
         <v>2319</v>
       </c>
-      <c r="B811" s="3" t="s">
+      <c r="B811" s="2" t="s">
         <v>2320</v>
       </c>
-      <c r="C811" s="3" t="s">
+      <c r="C811" s="2" t="s">
         <v>2321</v>
       </c>
     </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A812" s="2" t="s">
+    <row r="812" spans="1:3">
+      <c r="A812" s="3" t="s">
         <v>2322</v>
       </c>
-      <c r="B812" s="2" t="s">
+      <c r="B812" s="3" t="s">
         <v>2323</v>
       </c>
-      <c r="C812" s="2" t="s">
+      <c r="C812" s="3" t="s">
         <v>2324</v>
       </c>
     </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A813" s="3" t="s">
+    <row r="813" spans="1:3">
+      <c r="A813" s="2" t="s">
         <v>2325</v>
       </c>
-      <c r="B813" s="3" t="s">
+      <c r="B813" s="2" t="s">
         <v>2326</v>
       </c>
-      <c r="C813" s="3" t="s">
+      <c r="C813" s="2" t="s">
         <v>2327</v>
       </c>
     </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A814" s="2" t="s">
+    <row r="814" spans="1:3">
+      <c r="A814" s="3" t="s">
         <v>2328</v>
       </c>
-      <c r="B814" s="2" t="s">
+      <c r="B814" s="3" t="s">
         <v>2329</v>
       </c>
-      <c r="C814" s="2" t="s">
+      <c r="C814" s="3" t="s">
         <v>2330</v>
       </c>
     </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A815" s="3" t="s">
+    <row r="815" spans="1:3">
+      <c r="A815" s="2" t="s">
         <v>2331</v>
       </c>
-      <c r="B815" s="3" t="s">
+      <c r="B815" s="2" t="s">
         <v>2332</v>
       </c>
-      <c r="C815" s="3" t="s">
+      <c r="C815" s="2" t="s">
         <v>2333</v>
       </c>
     </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A816" s="2" t="s">
+    <row r="816" spans="1:3">
+      <c r="A816" s="3" t="s">
         <v>2334</v>
       </c>
-      <c r="B816" s="2" t="s">
+      <c r="B816" s="3" t="s">
         <v>2335</v>
       </c>
-      <c r="C816" s="2" t="s">
+      <c r="C816" s="3" t="s">
         <v>2336</v>
       </c>
     </row>
-    <row r="817" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A817" s="3" t="s">
+    <row r="817" spans="1:3">
+      <c r="A817" s="2" t="s">
         <v>2337</v>
       </c>
-      <c r="B817" s="3" t="s">
+      <c r="B817" s="2" t="s">
         <v>2338</v>
       </c>
-      <c r="C817" s="3" t="s">
+      <c r="C817" s="2" t="s">
         <v>2339</v>
       </c>
     </row>
-    <row r="818" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A818" s="2" t="s">
+    <row r="818" spans="1:3">
+      <c r="A818" s="3" t="s">
         <v>2340</v>
       </c>
-      <c r="B818" s="2" t="s">
+      <c r="B818" s="3" t="s">
         <v>2341</v>
       </c>
-      <c r="C818" s="2" t="s">
+      <c r="C818" s="3" t="s">
         <v>2342</v>
       </c>
     </row>
-    <row r="819" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A819" s="3" t="s">
+    <row r="819" spans="1:3">
+      <c r="A819" s="2" t="s">
         <v>2343</v>
       </c>
-      <c r="B819" s="3" t="s">
+      <c r="B819" s="2" t="s">
         <v>2344</v>
       </c>
-      <c r="C819" s="3" t="s">
+      <c r="C819" s="2" t="s">
         <v>2345</v>
       </c>
     </row>
-    <row r="820" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A820" s="2" t="s">
+    <row r="820" spans="1:3">
+      <c r="A820" s="3" t="s">
         <v>2346</v>
       </c>
-      <c r="B820" s="2" t="s">
+      <c r="B820" s="3" t="s">
         <v>2347</v>
       </c>
-      <c r="C820" s="2" t="s">
+      <c r="C820" s="3" t="s">
         <v>2348</v>
       </c>
     </row>
-    <row r="821" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A821" s="3" t="s">
+    <row r="821" spans="1:3">
+      <c r="A821" s="2" t="s">
         <v>2349</v>
       </c>
-      <c r="B821" s="3" t="s">
+      <c r="B821" s="2" t="s">
         <v>2350</v>
       </c>
-      <c r="C821" s="3" t="s">
+      <c r="C821" s="2" t="s">
         <v>2351</v>
       </c>
     </row>
-    <row r="822" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A822" s="2" t="s">
+    <row r="822" spans="1:3">
+      <c r="A822" s="3" t="s">
         <v>2352</v>
       </c>
-      <c r="B822" s="2" t="s">
+      <c r="B822" s="3" t="s">
         <v>2353</v>
       </c>
-      <c r="C822" s="2" t="s">
+      <c r="C822" s="3" t="s">
         <v>2354</v>
       </c>
     </row>
-    <row r="823" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A823" s="3" t="s">
+    <row r="823" spans="1:3">
+      <c r="A823" s="2" t="s">
         <v>2355</v>
       </c>
-      <c r="B823" s="3" t="s">
+      <c r="B823" s="2" t="s">
         <v>2356</v>
       </c>
-      <c r="C823" s="3" t="s">
+      <c r="C823" s="2" t="s">
         <v>2357</v>
       </c>
     </row>
-    <row r="824" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A824" s="2" t="s">
+    <row r="824" spans="1:3">
+      <c r="A824" s="3" t="s">
         <v>2358</v>
       </c>
-      <c r="B824" s="2" t="s">
+      <c r="B824" s="3" t="s">
         <v>2359</v>
       </c>
-      <c r="C824" s="2" t="s">
+      <c r="C824" s="3" t="s">
         <v>2360</v>
       </c>
     </row>
-    <row r="825" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A825" s="3" t="s">
+    <row r="825" spans="1:3">
+      <c r="A825" s="2" t="s">
         <v>2361</v>
       </c>
-      <c r="B825" s="3" t="s">
+      <c r="B825" s="2" t="s">
         <v>2362</v>
       </c>
-      <c r="C825" s="3" t="s">
+      <c r="C825" s="2" t="s">
         <v>2363</v>
       </c>
     </row>
-    <row r="826" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A826" s="2" t="s">
+    <row r="826" spans="1:3">
+      <c r="A826" s="3" t="s">
         <v>2364</v>
       </c>
-      <c r="B826" s="2" t="s">
+      <c r="B826" s="3" t="s">
         <v>2365</v>
       </c>
-      <c r="C826" s="2" t="s">
+      <c r="C826" s="3" t="s">
         <v>2366</v>
-      </c>
-    </row>
-    <row r="827" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A827" s="3" t="s">
-        <v>2367</v>
-      </c>
-      <c r="B827" s="3" t="s">
-        <v>2368</v>
-      </c>
-      <c r="C827" s="3" t="s">
-        <v>2369</v>
       </c>
     </row>
   </sheetData>
